--- a/maps/mediciones.xlsx
+++ b/maps/mediciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP VICTUS\Desktop\proyecto-iluminarias\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F559D734-B631-4E01-8711-102DEE05CED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87BE4B6-92EC-42BD-8403-0C71C516A80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Postes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="3146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6964" uniqueCount="3535">
   <si>
     <t>Facultad/Sector</t>
   </si>
@@ -9458,6 +9458,1173 @@
   </si>
   <si>
     <t>uuid:3676045e-ffa9-4aa8-9cca-9112a0e97dcd</t>
+  </si>
+  <si>
+    <t>Facultad de Ciencias Químicas</t>
+  </si>
+  <si>
+    <t>-0.1981978 -78.5049574 0 5</t>
+  </si>
+  <si>
+    <t>17794050297597165252032499465290-18_10_36.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759534061/attachments/attB5B5cvwx8RZuQwQRRpNrv/</t>
+  </si>
+  <si>
+    <t>0aab826a-ea5d-4ee2-9373-ff89363ed038</t>
+  </si>
+  <si>
+    <t>uuid:550583d6-7b10-4109-8097-1518cad47c28</t>
+  </si>
+  <si>
+    <t>-0.1986651 -78.504594 0 5</t>
+  </si>
+  <si>
+    <t>17794059607416845447307507509602-18_26_13.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759537413/attachments/att3jmzfvumcewkUUaYC6F5S/</t>
+  </si>
+  <si>
+    <t>4b5098f6-16bb-4968-9246-7996d50bd78c</t>
+  </si>
+  <si>
+    <t>uuid:4b5098f6-16bb-4968-9246-7996d50bd78c</t>
+  </si>
+  <si>
+    <t>-0.1986691 -78.5048347 0 5</t>
+  </si>
+  <si>
+    <t>17794056365923094437475544860471-18_20_44.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759537486/attachments/attuhRaNZDmRtBepExU7vf4p/</t>
+  </si>
+  <si>
+    <t>712c9a47-f542-497d-a7d5-5a60028078a5</t>
+  </si>
+  <si>
+    <t>uuid:712c9a47-f542-497d-a7d5-5a60028078a5</t>
+  </si>
+  <si>
+    <t>-0.1986185 -78.5050298 0 5</t>
+  </si>
+  <si>
+    <t>17794054203154883683908192931027-18_17_11.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759537661/attachments/attMkyZXu53euKWduGnTZckm/</t>
+  </si>
+  <si>
+    <t>1262084f-6ab9-4186-b6b6-0b88f1df52e8</t>
+  </si>
+  <si>
+    <t>uuid:2c1c1d0b-9ce3-4344-9190-09f6ff5e9542</t>
+  </si>
+  <si>
+    <t>-0.1984331 -78.5050067 0 5</t>
+  </si>
+  <si>
+    <t>17794052688668815555008500290478-18_14_35.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759537759/attachments/att8UhGWQw86yVfdC5wdv59w/</t>
+  </si>
+  <si>
+    <t>2c08232a-27bf-4c8a-8e81-c3eda2796982</t>
+  </si>
+  <si>
+    <t>uuid:2c08232a-27bf-4c8a-8e81-c3eda2796982</t>
+  </si>
+  <si>
+    <t>-0.1980294 -78.5048897 0 5</t>
+  </si>
+  <si>
+    <t>17794049515653949155050375335196-18_9_18.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759538587/attachments/attQVbS2EYPXUSjxgeZpWhXu/</t>
+  </si>
+  <si>
+    <t>72837887-ee8a-46eb-a780-349eb62e5cdc</t>
+  </si>
+  <si>
+    <t>uuid:a21ead52-7573-4816-a743-bfbf142d1514</t>
+  </si>
+  <si>
+    <t>-0.1979403 -78.5049189 0 5</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>IMG_20260521_180443-18_6_6.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759538754/attachments/att3HMBHS4x3U57JXzuGJW9r/</t>
+  </si>
+  <si>
+    <t>82717c72-ef19-4266-9c7e-101c6c6249c6</t>
+  </si>
+  <si>
+    <t>uuid:82717c72-ef19-4266-9c7e-101c6c6249c6</t>
+  </si>
+  <si>
+    <t>-0.1976291 -78.504895 0 5</t>
+  </si>
+  <si>
+    <t>IMG_20260521_180026-18_0_36.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759538891/attachments/attrwB4NPTAhNvBVivnK6oWc/</t>
+  </si>
+  <si>
+    <t>2d5b680e-3e21-45ae-8f08-ff518091b24f</t>
+  </si>
+  <si>
+    <t>uuid:2d5b680e-3e21-45ae-8f08-ff518091b24f</t>
+  </si>
+  <si>
+    <t>-0.1972932 -78.5044555 0 5</t>
+  </si>
+  <si>
+    <t>IMG_20260521_175812-17_58_22.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759538970/attachments/attEgovKPDB86m9bfXomT6yh/</t>
+  </si>
+  <si>
+    <t>9120d2a8-697e-4611-aa12-dafdc160422d</t>
+  </si>
+  <si>
+    <t>uuid:43b82bc8-3932-4de1-883a-4b12f7a72fda</t>
+  </si>
+  <si>
+    <t>-0.1972999 -78.5044545 0 5</t>
+  </si>
+  <si>
+    <t>IMG_20260521_175122-17_51_34.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759539287/attachments/atta22yJ7nhE9fsQChtSXzEU/</t>
+  </si>
+  <si>
+    <t>0c9c8c4b-8b35-45fc-b941-837f55dfe234</t>
+  </si>
+  <si>
+    <t>uuid:eb7a570b-e970-4d22-9151-015ade14d219</t>
+  </si>
+  <si>
+    <t>-0.1977321 -78.5047878 0 4</t>
+  </si>
+  <si>
+    <t>17794070122624699561346978346259-18_43_44.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759539760/attachments/att8MMfVyQ39gTrGaLeLugVp/</t>
+  </si>
+  <si>
+    <t>3a90745b-e657-4987-bd6d-2aa5d216a54f</t>
+  </si>
+  <si>
+    <t>uuid:3a90745b-e657-4987-bd6d-2aa5d216a54f</t>
+  </si>
+  <si>
+    <t>-0.1981371 -78.5047606 0 4</t>
+  </si>
+  <si>
+    <t>17794071677071810919367212597003-18_46_14.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759540023/attachments/attGUsMT2aJAYSQajymcfwg9/</t>
+  </si>
+  <si>
+    <t>208e478d-a89e-49cf-a443-6909e6b25a0e</t>
+  </si>
+  <si>
+    <t>uuid:d42f7f8a-789d-4096-8677-e11fc5c5c7c8</t>
+  </si>
+  <si>
+    <t>Facultad de Ingeniería en Geología, Minas, Petróleos y Ambiental</t>
+  </si>
+  <si>
+    <t>-0.1975021 -78.5050214 0 5</t>
+  </si>
+  <si>
+    <t>IG1</t>
+  </si>
+  <si>
+    <t>17794075301685028740139530969941-18_52_31.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759541471/attachments/attzJL7pcUxHnWMhHUqLRysP/</t>
+  </si>
+  <si>
+    <t>303f952a-8055-4ec6-8a1c-bc767f45232d</t>
+  </si>
+  <si>
+    <t>uuid:303f952a-8055-4ec6-8a1c-bc767f45232d</t>
+  </si>
+  <si>
+    <t>-0.1977163 -78.5054194 0 5</t>
+  </si>
+  <si>
+    <t>IG2</t>
+  </si>
+  <si>
+    <t>17794077331456130053708590960394-18_56_9.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759542176/attachments/attEYeWUwWYwpyK9RjVL4gd2/</t>
+  </si>
+  <si>
+    <t>6f227007-dc0c-4fdd-a9e0-cdd3f8869dd7</t>
+  </si>
+  <si>
+    <t>uuid:6f227007-dc0c-4fdd-a9e0-cdd3f8869dd7</t>
+  </si>
+  <si>
+    <t>-0.1978514 -78.5057044 0 5</t>
+  </si>
+  <si>
+    <t>IG4</t>
+  </si>
+  <si>
+    <t>1779407928494123721255380181007-18_59_14.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759543234/attachments/attXNvrGL7DAjzEW6QNNB3dk/</t>
+  </si>
+  <si>
+    <t>9280f81c-f0c3-42b4-8965-8c819390f0d8</t>
+  </si>
+  <si>
+    <t>uuid:9280f81c-f0c3-42b4-8965-8c819390f0d8</t>
+  </si>
+  <si>
+    <t>-0.1980589 -78.5059351 0 5</t>
+  </si>
+  <si>
+    <t>IG5</t>
+  </si>
+  <si>
+    <t>17794082646002908303402510461378-19_4_35.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759544055/attachments/attQxvGZf6Wwtjpxx9bYnMAx/</t>
+  </si>
+  <si>
+    <t>d87c03cc-c255-446b-aeae-ed3716e5ea54</t>
+  </si>
+  <si>
+    <t>uuid:d87c03cc-c255-446b-aeae-ed3716e5ea54</t>
+  </si>
+  <si>
+    <t>-0.198076 -78.505927 0 5</t>
+  </si>
+  <si>
+    <t>IG6</t>
+  </si>
+  <si>
+    <t>17794084943551013883807543380280-19_9_2.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759544554/attachments/attm4GATKKZaCXMCSTtkgYF2/</t>
+  </si>
+  <si>
+    <t>ddcbe241-7096-4b8e-8a07-daae1d9c514a</t>
+  </si>
+  <si>
+    <t>uuid:ddcbe241-7096-4b8e-8a07-daae1d9c514a</t>
+  </si>
+  <si>
+    <t>-0.1979919 -78.5057014 0 5</t>
+  </si>
+  <si>
+    <t>IG7</t>
+  </si>
+  <si>
+    <t>17794086212886645205060163992721-19_10_27.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759545341/attachments/attJf8zmk9Bs5s5AkM8p2BrS/</t>
+  </si>
+  <si>
+    <t>c3be0457-9511-4023-b0d1-c9e076b29feb</t>
+  </si>
+  <si>
+    <t>uuid:acdee777-b29b-4187-a17d-6370306d44f5</t>
+  </si>
+  <si>
+    <t>-0.1981699 -78.5057262 0 5</t>
+  </si>
+  <si>
+    <t>IG8</t>
+  </si>
+  <si>
+    <t>17794088453482180273709712486464-19_14_17.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759545629/attachments/attFtdndPQxVwxdQUKbA7Drv/</t>
+  </si>
+  <si>
+    <t>e21699f7-c5ea-4424-bcfd-e91552356535</t>
+  </si>
+  <si>
+    <t>uuid:83b7e2cf-d7f8-495e-90db-ba8360be379e</t>
+  </si>
+  <si>
+    <t>-0.1981522 -78.505629 0 5</t>
+  </si>
+  <si>
+    <t>IG9</t>
+  </si>
+  <si>
+    <t>17794089228757239075894527090615-19_15_35.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759545955/attachments/attiehxoCvsRtE82NzYzvicV/</t>
+  </si>
+  <si>
+    <t>3c3acd12-f797-45ad-a43e-bb3818298463</t>
+  </si>
+  <si>
+    <t>uuid:bfe2f0db-d01e-4570-9a6b-04561a25545d</t>
+  </si>
+  <si>
+    <t>-0.1982678 -78.505868 0 5</t>
+  </si>
+  <si>
+    <t>IG10</t>
+  </si>
+  <si>
+    <t>17794091283284539869087497419143-19_18_58.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759546516/attachments/attKGm224d7yiFNNr8ZTACQv/</t>
+  </si>
+  <si>
+    <t>222ceff0-72d2-4abe-8452-d4bfb300edf2</t>
+  </si>
+  <si>
+    <t>uuid:2e2d112d-ec2c-468a-bb47-bc4e1ba6a263</t>
+  </si>
+  <si>
+    <t>-0.1982628 -78.5058932 0 5</t>
+  </si>
+  <si>
+    <t>IG11</t>
+  </si>
+  <si>
+    <t>17794092179302984130215596662742-19_20_28.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759546712/attachments/attawHgnVz58hvVEwTyBTHGw/</t>
+  </si>
+  <si>
+    <t>38e212ef-1e50-4a1f-b4ac-5699e573a33f</t>
+  </si>
+  <si>
+    <t>uuid:8c3934d4-9e13-4280-96bc-148a840990ae</t>
+  </si>
+  <si>
+    <t>-0.1984965 -78.50557265 0 5</t>
+  </si>
+  <si>
+    <t>IG13</t>
+  </si>
+  <si>
+    <t>17794094687046859060422041796230-19_24_36.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759547482/attachments/attXbizBoZWpBJ6N9M9CcN6P/</t>
+  </si>
+  <si>
+    <t>9cb2875d-c3f7-496a-af9a-2620293a2b77</t>
+  </si>
+  <si>
+    <t>uuid:2b895528-fb46-4ac7-af50-823c34bf3e5e</t>
+  </si>
+  <si>
+    <t>-0.19855143 -78.5057205 0 5</t>
+  </si>
+  <si>
+    <t>IG14</t>
+  </si>
+  <si>
+    <t>17794096125493665503159998981679-19_26_58.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759547992/attachments/att472QkmvcRvPMzEFXerKkS/</t>
+  </si>
+  <si>
+    <t>72cd2c90-3cd0-466e-99be-caeb787b6478</t>
+  </si>
+  <si>
+    <t>uuid:ee750fc5-858d-44a3-9ef0-e0f7392fc492</t>
+  </si>
+  <si>
+    <t>-0.1984918 -78.5057242 0 5</t>
+  </si>
+  <si>
+    <t>IG15</t>
+  </si>
+  <si>
+    <t>17794096817715696312187454946396-19_28_10.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759548230/attachments/attgEAAD3ZwhESppKKKHUBRL/</t>
+  </si>
+  <si>
+    <t>caa098aa-16c6-4f31-a96b-0fe7f154fa44</t>
+  </si>
+  <si>
+    <t>uuid:8fe8a292-bb3b-4359-91b8-02ec4cc099f2</t>
+  </si>
+  <si>
+    <t>-0.1985196 -78.5055797 0 5</t>
+  </si>
+  <si>
+    <t>IG16</t>
+  </si>
+  <si>
+    <t>17794097416363752998263551613734-19_29_8.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759549783/attachments/att4gy2q9AsLTSmDWjNWy4RP/</t>
+  </si>
+  <si>
+    <t>3c39df0c-d3f1-4850-a161-1f08ef4d0138</t>
+  </si>
+  <si>
+    <t>uuid:3c39df0c-d3f1-4850-a161-1f08ef4d0138</t>
+  </si>
+  <si>
+    <t>-0.1985206 -78.5055535 0 5</t>
+  </si>
+  <si>
+    <t>IG17</t>
+  </si>
+  <si>
+    <t>17794104315481126619298895767635-19_40_45.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759550564/attachments/attcqPJzL29vgePkJFNLGoZ8/</t>
+  </si>
+  <si>
+    <t>70736658-f6cb-4d78-9da8-fd456f629194</t>
+  </si>
+  <si>
+    <t>uuid:c89f9f86-b8cb-4818-b0c3-90d662e65001</t>
+  </si>
+  <si>
+    <t>-0.1985062 -78.5053379 0 5</t>
+  </si>
+  <si>
+    <t>IG18</t>
+  </si>
+  <si>
+    <t>17794105914381867827107800370365-19_43_22.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759551014/attachments/attqwWTHhCUhdCRQfdBxnqfD/</t>
+  </si>
+  <si>
+    <t>387bd472-ebf0-4c71-a66e-8edc0de90ef2</t>
+  </si>
+  <si>
+    <t>uuid:c4ef20a8-58c7-4e59-854e-19156dd4ee07</t>
+  </si>
+  <si>
+    <t>-0.1987245 -78.5059699 0 5</t>
+  </si>
+  <si>
+    <t>IG20</t>
+  </si>
+  <si>
+    <t>1779410770945360071886754966929-19_46_22.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759551896/attachments/atttWoiJg3Rd3z6NDAfFdUdg/</t>
+  </si>
+  <si>
+    <t>c2ea0655-5634-4074-ae9e-1dda32ab8ddb</t>
+  </si>
+  <si>
+    <t>uuid:cce457c0-cf02-4783-bec8-dde4104be9b9</t>
+  </si>
+  <si>
+    <t>-0.1990232 -78.50592 0 5</t>
+  </si>
+  <si>
+    <t>IG21</t>
+  </si>
+  <si>
+    <t>17794109205321667256459659185815-19_48_52.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759552387/attachments/attAGnw4T8N6PEZBBiA8XbRK/</t>
+  </si>
+  <si>
+    <t>65130d25-ba99-4db5-ad96-5a2d0fa1e582</t>
+  </si>
+  <si>
+    <t>uuid:65130d25-ba99-4db5-ad96-5a2d0fa1e582</t>
+  </si>
+  <si>
+    <t>-0.1993159 -78.5058285 0 5</t>
+  </si>
+  <si>
+    <t>IG22</t>
+  </si>
+  <si>
+    <t>17794110375138205173582638654646-19_50_47.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759552948/attachments/attrW3JMQEF4JcSPYhYjga94/</t>
+  </si>
+  <si>
+    <t>a58d9574-7c2f-4d96-8c08-c34add53507c</t>
+  </si>
+  <si>
+    <t>uuid:a58d9574-7c2f-4d96-8c08-c34add53507c</t>
+  </si>
+  <si>
+    <t>-0.1991258 -78.5054892 0 5</t>
+  </si>
+  <si>
+    <t>IG3</t>
+  </si>
+  <si>
+    <t>17794112660658586709611581736265-19_54_37.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759553510/attachments/attUADUj4CFhuzcaiLYfziqB/</t>
+  </si>
+  <si>
+    <t>a5750adc-553a-4ab1-979a-a2b07f585657</t>
+  </si>
+  <si>
+    <t>uuid:e5cf098a-6d87-4111-94bc-00009744dffa</t>
+  </si>
+  <si>
+    <t>-0.1990789 -78.5053544 0 5</t>
+  </si>
+  <si>
+    <t>IG23</t>
+  </si>
+  <si>
+    <t>17794114424443611567865299213894-19_57_31.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759554371/attachments/attBqvrSnWRihkdMJLDRqPBQ/</t>
+  </si>
+  <si>
+    <t>4ff26828-4a9b-4a1d-a8b8-b8671953bd34</t>
+  </si>
+  <si>
+    <t>uuid:4ff26828-4a9b-4a1d-a8b8-b8671953bd34</t>
+  </si>
+  <si>
+    <t>-0.1991241 -78.5053691 0 5</t>
+  </si>
+  <si>
+    <t>IG24</t>
+  </si>
+  <si>
+    <t>17794115971105116047789575791098-20_0_4.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759554785/attachments/atttRxpQTjwfq4egMwHQY8CL/</t>
+  </si>
+  <si>
+    <t>ec1efaba-94b1-4cb5-82e8-424fbc131048</t>
+  </si>
+  <si>
+    <t>uuid:ec1efaba-94b1-4cb5-82e8-424fbc131048</t>
+  </si>
+  <si>
+    <t>-0.1990963 -78.5049631 0 5</t>
+  </si>
+  <si>
+    <t>IG25</t>
+  </si>
+  <si>
+    <t>17794116714108269150362261960453-20_1_19.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759555263/attachments/attChnQgmTu8VE7t8CZZo8nr/</t>
+  </si>
+  <si>
+    <t>9324eff2-5a50-4bef-8559-0a8a127f3d07</t>
+  </si>
+  <si>
+    <t>uuid:9324eff2-5a50-4bef-8559-0a8a127f3d07</t>
+  </si>
+  <si>
+    <t>-0.1990504 -78.5049792 0 5</t>
+  </si>
+  <si>
+    <t>IG26</t>
+  </si>
+  <si>
+    <t>17794117412973389660922480219773-20_2_29.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759555529/attachments/attqBzgThh7KsBAHqWsezRqF/</t>
+  </si>
+  <si>
+    <t>67c94c4a-040a-4982-bd40-252e48b8bf97</t>
+  </si>
+  <si>
+    <t>uuid:67c94c4a-040a-4982-bd40-252e48b8bf97</t>
+  </si>
+  <si>
+    <t>-0.198223 -78.505617 0 0</t>
+  </si>
+  <si>
+    <t>IG27</t>
+  </si>
+  <si>
+    <t>17794119583605814334770804097165-20_6_6.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759556485/attachments/attQ9Ty2urJjJM36qogXbxwo/</t>
+  </si>
+  <si>
+    <t>a0a86162-4831-47e7-94fe-6183a1046bb2</t>
+  </si>
+  <si>
+    <t>uuid:1a669e65-419a-42d0-a4d6-d7c9f8d1cb9e</t>
+  </si>
+  <si>
+    <t>-0.1979859 -78.5052417 0 5</t>
+  </si>
+  <si>
+    <t>IG12</t>
+  </si>
+  <si>
+    <t>17794120801988654233362140595614-20_8_24.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759556836/attachments/attus5yJurGmzY4k5LgrUux2/</t>
+  </si>
+  <si>
+    <t>53cda506-8805-41cc-90ff-528c06dc9a89</t>
+  </si>
+  <si>
+    <t>uuid:4a0ad49e-6159-45b4-9df7-d5714d64b384</t>
+  </si>
+  <si>
+    <t>IG19</t>
+  </si>
+  <si>
+    <t>17794122257478629517873703992774-20_10_34.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759557343/attachments/attojtR5XKdDBRbMH6xrw7nr/</t>
+  </si>
+  <si>
+    <t>48a29fb7-ca7e-48a2-9c76-62ce83e2534f</t>
+  </si>
+  <si>
+    <t>uuid:97258b3f-7e96-479d-8bc7-6f1b8a11fd0d</t>
+  </si>
+  <si>
+    <t>-0.1979195 -78.50544053 0 5</t>
+  </si>
+  <si>
+    <t>17794122907678960700732930170400-20_11_36.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/759557580/attachments/attsCELUvdjGi4B8tNP7sFF8/</t>
+  </si>
+  <si>
+    <t>1bb1e4bc-044a-4fa3-8a53-e83b630c3fae</t>
+  </si>
+  <si>
+    <t>uuid:28595f05-879c-4e57-938a-c1b8bac1abca</t>
+  </si>
+  <si>
+    <t>Facultad de Ciencias Agrícolas</t>
+  </si>
+  <si>
+    <t>-0.19912 -78.505993 2884.800048828125 21.26799964904785</t>
+  </si>
+  <si>
+    <t>Agro004</t>
+  </si>
+  <si>
+    <t>1000273527-18_41_33.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768756706/attachments/attJZX6u6NChVkyohWgZZGBn/</t>
+  </si>
+  <si>
+    <t>b6e5fe5f-b195-4228-a7fa-88b22a0bd48a</t>
+  </si>
+  <si>
+    <t>uuid:b6e5fe5f-b195-4228-a7fa-88b22a0bd48a</t>
+  </si>
+  <si>
+    <t>Facultad de Medicina Veterinaria y Zootecnia</t>
+  </si>
+  <si>
+    <t>-0.1974 -78.506193 2880.60009765625 17.238000869750977</t>
+  </si>
+  <si>
+    <t>Vet012</t>
+  </si>
+  <si>
+    <t>1000273499-18_28_30.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768757122/attachments/att4EQwMXec77po8sZdvqKEs/</t>
+  </si>
+  <si>
+    <t>dfc6dc99-e9ce-4ce3-b0bb-26cd957cb9c5</t>
+  </si>
+  <si>
+    <t>uuid:dfc6dc99-e9ce-4ce3-b0bb-26cd957cb9c5</t>
+  </si>
+  <si>
+    <t>-0.197441 -78.506643 2886.7001953125 17.55900001525879</t>
+  </si>
+  <si>
+    <t>Vet011</t>
+  </si>
+  <si>
+    <t>1000273498-18_27_15.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768757252/attachments/atthbnSL6gtGrhSdJDQ2xomE/</t>
+  </si>
+  <si>
+    <t>097c3a62-1279-49b6-b372-d3e0d26dc30c</t>
+  </si>
+  <si>
+    <t>uuid:097c3a62-1279-49b6-b372-d3e0d26dc30c</t>
+  </si>
+  <si>
+    <t>-0.197451 -78.506998 2889.2001953125 31.777999877929688</t>
+  </si>
+  <si>
+    <t>Vet010</t>
+  </si>
+  <si>
+    <t>1000273497-18_25_23.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768757399/attachments/attvaLtKTPucz7WU4aMUcoWY/</t>
+  </si>
+  <si>
+    <t>0a90a70f-503f-41ea-9fd4-07370c40c549</t>
+  </si>
+  <si>
+    <t>uuid:ee4224bc-44e5-4416-b751-ff3d721c8f64</t>
+  </si>
+  <si>
+    <t>-0.198327 -78.506164 2883.2001953125 26.136999130249023</t>
+  </si>
+  <si>
+    <t>Agro001</t>
+  </si>
+  <si>
+    <t>1000273477-18_31_18.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768757859/attachments/attL7TKfRSXidTLBVxZuEQfQ/</t>
+  </si>
+  <si>
+    <t>aa119f92-5a18-4f19-9bf5-ad9d3fdb5558</t>
+  </si>
+  <si>
+    <t>uuid:aa119f92-5a18-4f19-9bf5-ad9d3fdb5558</t>
+  </si>
+  <si>
+    <t>-0.19852 -78.506256 2884.300048828125 19.235000610351562</t>
+  </si>
+  <si>
+    <t>Agro002</t>
+  </si>
+  <si>
+    <t>1000273478-17_54_55.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768758025/attachments/attte28zDurQAyNH879GTerD/</t>
+  </si>
+  <si>
+    <t>e78f776b-16be-4595-b0d2-b6690b6ee349</t>
+  </si>
+  <si>
+    <t>uuid:e78f776b-16be-4595-b0d2-b6690b6ee349</t>
+  </si>
+  <si>
+    <t>-0.198554 -78.506304 2884.400146484375 18.1560001373291</t>
+  </si>
+  <si>
+    <t>18:24:00.000-05:00</t>
+  </si>
+  <si>
+    <t>Agro003</t>
+  </si>
+  <si>
+    <t>1000273521-18_38_48.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768758265/attachments/attgfpMpXKCzqvhDrdvsLGvV/</t>
+  </si>
+  <si>
+    <t>913d4065-9174-4be1-955d-1bb55deb0ab4</t>
+  </si>
+  <si>
+    <t>uuid:913d4065-9174-4be1-955d-1bb55deb0ab4</t>
+  </si>
+  <si>
+    <t>-0.199132 -78.505895 2891.2001953125 15.013999938964844</t>
+  </si>
+  <si>
+    <t>Agro005</t>
+  </si>
+  <si>
+    <t>1000273528-18_43_2.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768758598/attachments/attnSWMK75ACmpx8Q2yKqjqQ/</t>
+  </si>
+  <si>
+    <t>cc7eed47-0d1b-4670-b334-e812b4818794</t>
+  </si>
+  <si>
+    <t>uuid:cc7eed47-0d1b-4670-b334-e812b4818794</t>
+  </si>
+  <si>
+    <t>-0.198748 -78.506633 2888.400146484375 22.649999618530273</t>
+  </si>
+  <si>
+    <t>Agro006</t>
+  </si>
+  <si>
+    <t>1000273529-18_45_8.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768758744/attachments/attjrVPaWivnPwx9LfAmFJKJ/</t>
+  </si>
+  <si>
+    <t>50544927-f308-4fba-bc5a-408f9f6445ce</t>
+  </si>
+  <si>
+    <t>uuid:50544927-f308-4fba-bc5a-408f9f6445ce</t>
+  </si>
+  <si>
+    <t>-0.198699 -78.506924 2892.2001953125 24.13800048828125</t>
+  </si>
+  <si>
+    <t>Agro007</t>
+  </si>
+  <si>
+    <t>1000273530-18_46_56.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768758967/attachments/attcP8APmkJFzZdsTvkaZyPv/</t>
+  </si>
+  <si>
+    <t>df787f06-101d-423b-b5d1-7cf7c691db31</t>
+  </si>
+  <si>
+    <t>uuid:df787f06-101d-423b-b5d1-7cf7c691db31</t>
+  </si>
+  <si>
+    <t>-0.198573 -78.507104 2892.60009765625 23.808000564575195</t>
+  </si>
+  <si>
+    <t>Agro008</t>
+  </si>
+  <si>
+    <t>1000273484-18_6_41.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768759134/attachments/attkcdcia9hsRKJVTXTSFf3t/</t>
+  </si>
+  <si>
+    <t>727fc235-57ab-414f-8fd9-a6c76f03e68b</t>
+  </si>
+  <si>
+    <t>uuid:727fc235-57ab-414f-8fd9-a6c76f03e68b</t>
+  </si>
+  <si>
+    <t>-0.198607 -78.507062 2892.60009765625 22.194000244140625</t>
+  </si>
+  <si>
+    <t>Agro009</t>
+  </si>
+  <si>
+    <t>1000273531-18_49_51.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768759574/attachments/atta4Ni9UCihEpa5C7WqHjFW/</t>
+  </si>
+  <si>
+    <t>f18e4603-3768-4df8-9349-eb41238e90c1</t>
+  </si>
+  <si>
+    <t>uuid:f18e4603-3768-4df8-9349-eb41238e90c1</t>
+  </si>
+  <si>
+    <t>-0.198759 -78.507434 2892.60009765625 51.06999969482422</t>
+  </si>
+  <si>
+    <t>Agro010</t>
+  </si>
+  <si>
+    <t>1000273532-18_51_21.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768759865/attachments/atth3shworh5tx2fkJNwiKPC/</t>
+  </si>
+  <si>
+    <t>6179eaf9-f984-4e7a-8ba5-cf620019ecbc</t>
+  </si>
+  <si>
+    <t>uuid:6179eaf9-f984-4e7a-8ba5-cf620019ecbc</t>
+  </si>
+  <si>
+    <t>-0.198458 -78.507143 2889.000244140625 38.70600128173828</t>
+  </si>
+  <si>
+    <t>Agro011</t>
+  </si>
+  <si>
+    <t>1000273535-18_52_34.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768760184/attachments/attDW4GR9iPpqKUVcHeEoY4V/</t>
+  </si>
+  <si>
+    <t>e4f7b029-cc94-4334-8b9a-3e69ad77b04d</t>
+  </si>
+  <si>
+    <t>uuid:e4f7b029-cc94-4334-8b9a-3e69ad77b04d</t>
+  </si>
+  <si>
+    <t>-0.198465 -78.507142 2893.500244140625 37.45500183105469</t>
+  </si>
+  <si>
+    <t>Agro012</t>
+  </si>
+  <si>
+    <t>1000273488-18_13_0.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768760477/attachments/att4oJqF2RxPGpPdAXAoSTGm/</t>
+  </si>
+  <si>
+    <t>cf61b662-15d9-4f1f-b080-b8cdc0252cf8</t>
+  </si>
+  <si>
+    <t>uuid:cf61b662-15d9-4f1f-b080-b8cdc0252cf8</t>
+  </si>
+  <si>
+    <t>-0.198544 -78.506865 2888.500244140625 24.358999252319336</t>
+  </si>
+  <si>
+    <t>18:14:00.000-05:00</t>
+  </si>
+  <si>
+    <t>Agro013</t>
+  </si>
+  <si>
+    <t>1000273489-18_14_29.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768760641/attachments/attgMosCXggjdmzhdNQxSZ5R/</t>
+  </si>
+  <si>
+    <t>4f15a87b-db05-4dfe-9cac-9af3ec49b9d0</t>
+  </si>
+  <si>
+    <t>uuid:4f15a87b-db05-4dfe-9cac-9af3ec49b9d0</t>
+  </si>
+  <si>
+    <t>-0.198562 -78.506529 2888.7001953125 19.408000946044922</t>
+  </si>
+  <si>
+    <t>Agro014</t>
+  </si>
+  <si>
+    <t>1000273490-18_15_24.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768760853/attachments/attdFxpdkCEKhqNKQh6DkDdB/</t>
+  </si>
+  <si>
+    <t>8dbeda59-be12-41e4-8edc-ccb4fef0be09</t>
+  </si>
+  <si>
+    <t>uuid:8dbeda59-be12-41e4-8edc-ccb4fef0be09</t>
+  </si>
+  <si>
+    <t>-0.198498 -78.506697 2888.900146484375 40.29999923706055</t>
+  </si>
+  <si>
+    <t>Vet001</t>
+  </si>
+  <si>
+    <t>1000273491-18_17_17.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768761060/attachments/attz4ews64TGrMSnyvtBEkNp/</t>
+  </si>
+  <si>
+    <t>4ae1a280-7cf9-4f3b-9922-dfa51ef1cff6</t>
+  </si>
+  <si>
+    <t>uuid:4ae1a280-7cf9-4f3b-9922-dfa51ef1cff6</t>
+  </si>
+  <si>
+    <t>-0.19854 -78.506857 2893.500244140625 19.10700035095215</t>
+  </si>
+  <si>
+    <t>Vet002</t>
+  </si>
+  <si>
+    <t>1000273492-18_18_40.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768761384/attachments/attUnfLa42hsCTwZMAZHRdww/</t>
+  </si>
+  <si>
+    <t>1c93e1c6-f9de-4440-8110-b26104da5e5b</t>
+  </si>
+  <si>
+    <t>uuid:1c93e1c6-f9de-4440-8110-b26104da5e5b</t>
+  </si>
+  <si>
+    <t>-0.198213 -78.506922 2889.000244140625 40.900001525878906</t>
+  </si>
+  <si>
+    <t>Vet003</t>
+  </si>
+  <si>
+    <t>1000273536-18_58_12.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768761711/attachments/attxyHmRBe5LcKzo5cEyQ9uH/</t>
+  </si>
+  <si>
+    <t>3f2a289a-29e6-42f2-b966-c1c39917f950</t>
+  </si>
+  <si>
+    <t>uuid:3f2a289a-29e6-42f2-b966-c1c39917f950</t>
+  </si>
+  <si>
+    <t>-0.198176 -78.50718 2888.900146484375 49.034000396728516</t>
+  </si>
+  <si>
+    <t>Vet004</t>
+  </si>
+  <si>
+    <t>1000273494-18_19_59.jpg</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/768762214/attachments/attRgrsmSMX9aXkfHQ94XGNg/</t>
+  </si>
+  <si>
+    <t>00c5ebfb-6124-4c18-b5da-ddca2aff228f</t>
+  </si>
+  <si>
+    <t>uuid:00c5ebfb-6124-4c18-b5da-ddca2aff228f</t>
+  </si>
+  <si>
+    <t>-0.197702 -78.507028 2889.2001953125 32.38600158691406</t>
+  </si>
+  <si>
+    <t>Vet005</t>
+  </si>
+  <si>
+    <t>imagen_2026-06-03_164333795-16_43_33.png</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/770201879/attachments/attqzZJVPUWrFiMVU95Mu8eu/</t>
+  </si>
+  <si>
+    <t>d61f758a-016c-41ca-964f-b4a5f24052cb</t>
+  </si>
+  <si>
+    <t>uuid:4fb13a33-2530-42e0-b29b-19e200909e9d</t>
+  </si>
+  <si>
+    <t>-0.197853 -78.506842 2888.900146484375 7.39900016784668</t>
+  </si>
+  <si>
+    <t>Vet007</t>
+  </si>
+  <si>
+    <t>imagen_2026-06-03_164508104-16_45_8.png</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/770201932/attachments/attFtzgVHSRDEKJhchTEouAw/</t>
+  </si>
+  <si>
+    <t>c42ef76d-c637-4f41-8b80-03a6bed072d1</t>
+  </si>
+  <si>
+    <t>uuid:75ce0cfa-c1c5-48d4-9555-aab0d7a55526</t>
+  </si>
+  <si>
+    <t>-0.197994 -78.506836 2888.900146484375 16.218000411987305</t>
+  </si>
+  <si>
+    <t>Vet008</t>
+  </si>
+  <si>
+    <t>imagen_2026-06-03_164752567-16_47_52.png</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/770201989/attachments/attXJGV8szZTyaNcpk8HtNjY/</t>
+  </si>
+  <si>
+    <t>089854df-aa5c-4186-8adf-2e138eced321</t>
+  </si>
+  <si>
+    <t>uuid:fcce70fe-9af7-4da1-bec4-553c31641ef0</t>
+  </si>
+  <si>
+    <t>-0.197748 -78.506772 2888.900146484375 7.39900016784668</t>
+  </si>
+  <si>
+    <t>Vet006</t>
+  </si>
+  <si>
+    <t>imagen_2026-06-03_165622768-16_56_22.png</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/770202012/attachments/attMvBox9zg7sSdg2nbjrUf4/</t>
+  </si>
+  <si>
+    <t>395a331f-3198-4c3f-af4b-d33bc87dfd45</t>
+  </si>
+  <si>
+    <t>uuid:79ebcab8-5764-4afa-8c58-9a36d66dd259</t>
+  </si>
+  <si>
+    <t>-0.198088 -78.506695 2888.7001953125 8.23900032043457</t>
+  </si>
+  <si>
+    <t>Vet009</t>
+  </si>
+  <si>
+    <t>imagen_2026-06-03_164944558-16_49_44.png</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aMA6LiTGxeVVbQDCxZmC7C/data/770202059/attachments/attDNMgB3xnExRUCi2X6cuni/</t>
+  </si>
+  <si>
+    <t>8a4709db-e752-4e5c-a601-1b4551a5b308</t>
+  </si>
+  <si>
+    <t>uuid:5aeb90e6-c689-4d42-ace2-3a615b34477b</t>
   </si>
 </sst>
 </file>
@@ -9859,21 +11026,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA452"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AA518"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.88671875" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9956,7 +11123,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -10024,7 +11191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -10092,7 +11259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -10160,7 +11327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -10228,7 +11395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -10296,7 +11463,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -10364,7 +11531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -10429,7 +11596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -10494,7 +11661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -10559,7 +11726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -10624,7 +11791,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -10689,7 +11856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -10757,7 +11924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -10825,7 +11992,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -10893,7 +12060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -10958,7 +12125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -11026,7 +12193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -11094,7 +12261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -11162,7 +12329,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -11227,7 +12394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -11292,7 +12459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>135</v>
       </c>
@@ -11360,7 +12527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -11428,7 +12595,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -11496,7 +12663,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -11564,7 +12731,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -11632,7 +12799,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -11700,7 +12867,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -11768,7 +12935,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -11836,7 +13003,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -11901,7 +13068,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -11966,7 +13133,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -12034,7 +13201,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>193</v>
       </c>
@@ -12105,7 +13272,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>193</v>
       </c>
@@ -12170,7 +13337,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>193</v>
       </c>
@@ -12238,7 +13405,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>193</v>
       </c>
@@ -12309,7 +13476,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -12374,7 +13541,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>193</v>
       </c>
@@ -12439,7 +13606,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>193</v>
       </c>
@@ -12504,7 +13671,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>193</v>
       </c>
@@ -12569,7 +13736,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>193</v>
       </c>
@@ -12634,7 +13801,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>193</v>
       </c>
@@ -12699,7 +13866,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>193</v>
       </c>
@@ -12764,7 +13931,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>193</v>
       </c>
@@ -12829,7 +13996,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>272</v>
       </c>
@@ -12900,7 +14067,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -12965,7 +14132,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -13036,7 +14203,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>193</v>
       </c>
@@ -13107,7 +14274,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>296</v>
       </c>
@@ -13178,7 +14345,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>296</v>
       </c>
@@ -13243,7 +14410,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>296</v>
       </c>
@@ -13308,7 +14475,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>296</v>
       </c>
@@ -13379,7 +14546,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>296</v>
       </c>
@@ -13450,7 +14617,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>296</v>
       </c>
@@ -13521,7 +14688,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>296</v>
       </c>
@@ -13592,7 +14759,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>296</v>
       </c>
@@ -13663,7 +14830,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>296</v>
       </c>
@@ -13734,7 +14901,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>296</v>
       </c>
@@ -13805,7 +14972,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>296</v>
       </c>
@@ -13870,7 +15037,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>296</v>
       </c>
@@ -13935,7 +15102,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>296</v>
       </c>
@@ -14000,7 +15167,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>296</v>
       </c>
@@ -14065,7 +15232,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>296</v>
       </c>
@@ -14130,7 +15297,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>296</v>
       </c>
@@ -14195,7 +15362,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>296</v>
       </c>
@@ -14260,7 +15427,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>296</v>
       </c>
@@ -14331,7 +15498,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>296</v>
       </c>
@@ -14402,7 +15569,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>296</v>
       </c>
@@ -14467,7 +15634,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>296</v>
       </c>
@@ -14532,7 +15699,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>296</v>
       </c>
@@ -14597,7 +15764,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>296</v>
       </c>
@@ -14662,7 +15829,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>435</v>
       </c>
@@ -14727,7 +15894,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>435</v>
       </c>
@@ -14792,7 +15959,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>435</v>
       </c>
@@ -14860,7 +16027,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>435</v>
       </c>
@@ -14925,7 +16092,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>435</v>
       </c>
@@ -14990,7 +16157,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>435</v>
       </c>
@@ -15061,7 +16228,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>435</v>
       </c>
@@ -15126,7 +16293,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>435</v>
       </c>
@@ -15197,7 +16364,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>435</v>
       </c>
@@ -15268,7 +16435,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>435</v>
       </c>
@@ -15339,7 +16506,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>435</v>
       </c>
@@ -15410,7 +16577,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>435</v>
       </c>
@@ -15481,7 +16648,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>435</v>
       </c>
@@ -15546,7 +16713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>435</v>
       </c>
@@ -15611,7 +16778,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>435</v>
       </c>
@@ -15682,7 +16849,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>435</v>
       </c>
@@ -15753,7 +16920,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>435</v>
       </c>
@@ -15824,7 +16991,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>435</v>
       </c>
@@ -15895,7 +17062,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>435</v>
       </c>
@@ -15966,7 +17133,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>435</v>
       </c>
@@ -16037,7 +17204,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>435</v>
       </c>
@@ -16102,7 +17269,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>435</v>
       </c>
@@ -16173,7 +17340,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>435</v>
       </c>
@@ -16244,7 +17411,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>435</v>
       </c>
@@ -16315,7 +17482,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>272</v>
       </c>
@@ -16380,7 +17547,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>272</v>
       </c>
@@ -16445,7 +17612,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>272</v>
       </c>
@@ -16510,7 +17677,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>272</v>
       </c>
@@ -16575,7 +17742,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>272</v>
       </c>
@@ -16640,7 +17807,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>272</v>
       </c>
@@ -16705,7 +17872,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>272</v>
       </c>
@@ -16767,7 +17934,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>272</v>
       </c>
@@ -16832,7 +17999,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>272</v>
       </c>
@@ -16897,7 +18064,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>272</v>
       </c>
@@ -16962,7 +18129,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>272</v>
       </c>
@@ -17027,7 +18194,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>272</v>
       </c>
@@ -17092,7 +18259,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>272</v>
       </c>
@@ -17157,7 +18324,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>272</v>
       </c>
@@ -17222,7 +18389,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>272</v>
       </c>
@@ -17284,7 +18451,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>135</v>
       </c>
@@ -17349,7 +18516,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>135</v>
       </c>
@@ -17414,7 +18581,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>135</v>
       </c>
@@ -17479,7 +18646,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>272</v>
       </c>
@@ -17544,7 +18711,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>272</v>
       </c>
@@ -17609,7 +18776,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>135</v>
       </c>
@@ -17674,7 +18841,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>296</v>
       </c>
@@ -17745,7 +18912,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>296</v>
       </c>
@@ -17816,7 +18983,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>296</v>
       </c>
@@ -17887,7 +19054,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>296</v>
       </c>
@@ -17958,7 +19125,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>193</v>
       </c>
@@ -18029,7 +19196,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>193</v>
       </c>
@@ -18100,7 +19267,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>193</v>
       </c>
@@ -18171,7 +19338,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>435</v>
       </c>
@@ -18242,7 +19409,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>435</v>
       </c>
@@ -18313,7 +19480,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>435</v>
       </c>
@@ -18384,7 +19551,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>435</v>
       </c>
@@ -18449,7 +19616,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>435</v>
       </c>
@@ -18514,7 +19681,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>435</v>
       </c>
@@ -18579,7 +19746,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>435</v>
       </c>
@@ -18650,7 +19817,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>435</v>
       </c>
@@ -18721,7 +19888,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>435</v>
       </c>
@@ -18786,7 +19953,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>435</v>
       </c>
@@ -18857,7 +20024,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>435</v>
       </c>
@@ -18928,7 +20095,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>435</v>
       </c>
@@ -18999,7 +20166,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>435</v>
       </c>
@@ -19070,7 +20237,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>435</v>
       </c>
@@ -19141,7 +20308,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>435</v>
       </c>
@@ -19212,7 +20379,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>435</v>
       </c>
@@ -19283,7 +20450,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>272</v>
       </c>
@@ -19351,7 +20518,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>272</v>
       </c>
@@ -19416,7 +20583,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>272</v>
       </c>
@@ -19481,7 +20648,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>272</v>
       </c>
@@ -19546,7 +20713,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>272</v>
       </c>
@@ -19611,7 +20778,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>272</v>
       </c>
@@ -19676,7 +20843,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>272</v>
       </c>
@@ -19741,7 +20908,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>272</v>
       </c>
@@ -19806,7 +20973,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>866</v>
       </c>
@@ -19877,7 +21044,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>866</v>
       </c>
@@ -19948,7 +21115,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>866</v>
       </c>
@@ -20019,7 +21186,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>866</v>
       </c>
@@ -20090,7 +21257,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>866</v>
       </c>
@@ -20161,7 +21328,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>866</v>
       </c>
@@ -20232,7 +21399,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>866</v>
       </c>
@@ -20303,7 +21470,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>866</v>
       </c>
@@ -20374,7 +21541,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>866</v>
       </c>
@@ -20442,7 +21609,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>866</v>
       </c>
@@ -20513,7 +21680,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>866</v>
       </c>
@@ -20584,7 +21751,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>866</v>
       </c>
@@ -20655,7 +21822,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>866</v>
       </c>
@@ -20726,7 +21893,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>866</v>
       </c>
@@ -20797,7 +21964,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>866</v>
       </c>
@@ -20868,7 +22035,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>866</v>
       </c>
@@ -20939,7 +22106,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>866</v>
       </c>
@@ -21010,7 +22177,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>866</v>
       </c>
@@ -21081,7 +22248,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>866</v>
       </c>
@@ -21152,7 +22319,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>866</v>
       </c>
@@ -21223,7 +22390,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>866</v>
       </c>
@@ -21294,7 +22461,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>866</v>
       </c>
@@ -21365,7 +22532,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>866</v>
       </c>
@@ -21436,7 +22603,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>866</v>
       </c>
@@ -21507,7 +22674,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>866</v>
       </c>
@@ -21578,7 +22745,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>866</v>
       </c>
@@ -21649,7 +22816,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>866</v>
       </c>
@@ -21720,7 +22887,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>866</v>
       </c>
@@ -21791,7 +22958,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>866</v>
       </c>
@@ -21862,7 +23029,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>866</v>
       </c>
@@ -21933,7 +23100,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>866</v>
       </c>
@@ -22004,7 +23171,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>866</v>
       </c>
@@ -22075,7 +23242,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>866</v>
       </c>
@@ -22146,7 +23313,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>866</v>
       </c>
@@ -22214,7 +23381,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>866</v>
       </c>
@@ -22285,7 +23452,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>866</v>
       </c>
@@ -22356,7 +23523,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>866</v>
       </c>
@@ -22427,7 +23594,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>866</v>
       </c>
@@ -22498,7 +23665,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>866</v>
       </c>
@@ -22569,7 +23736,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>866</v>
       </c>
@@ -22640,7 +23807,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1118</v>
       </c>
@@ -22711,7 +23878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1118</v>
       </c>
@@ -22782,7 +23949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1118</v>
       </c>
@@ -22853,7 +24020,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1118</v>
       </c>
@@ -22924,7 +24091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1118</v>
       </c>
@@ -22995,7 +24162,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1118</v>
       </c>
@@ -23066,7 +24233,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1118</v>
       </c>
@@ -23137,7 +24304,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1118</v>
       </c>
@@ -23208,7 +24375,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1118</v>
       </c>
@@ -23279,7 +24446,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1118</v>
       </c>
@@ -23350,7 +24517,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1118</v>
       </c>
@@ -23421,7 +24588,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1118</v>
       </c>
@@ -23492,7 +24659,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1118</v>
       </c>
@@ -23563,7 +24730,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1118</v>
       </c>
@@ -23634,7 +24801,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1204</v>
       </c>
@@ -23705,7 +24872,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1204</v>
       </c>
@@ -23773,7 +24940,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1204</v>
       </c>
@@ -23844,7 +25011,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1204</v>
       </c>
@@ -23915,7 +25082,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1204</v>
       </c>
@@ -23986,7 +25153,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1204</v>
       </c>
@@ -24057,7 +25224,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1204</v>
       </c>
@@ -24128,7 +25295,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1204</v>
       </c>
@@ -24199,7 +25366,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1204</v>
       </c>
@@ -24270,7 +25437,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1204</v>
       </c>
@@ -24341,7 +25508,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1204</v>
       </c>
@@ -24412,7 +25579,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1204</v>
       </c>
@@ -24483,7 +25650,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1204</v>
       </c>
@@ -24554,7 +25721,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1204</v>
       </c>
@@ -24625,7 +25792,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1204</v>
       </c>
@@ -24696,7 +25863,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1204</v>
       </c>
@@ -24767,7 +25934,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1204</v>
       </c>
@@ -24838,7 +26005,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1204</v>
       </c>
@@ -24909,7 +26076,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1204</v>
       </c>
@@ -24980,7 +26147,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1204</v>
       </c>
@@ -25051,7 +26218,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1204</v>
       </c>
@@ -25122,7 +26289,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1204</v>
       </c>
@@ -25193,7 +26360,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1204</v>
       </c>
@@ -25264,7 +26431,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1204</v>
       </c>
@@ -25335,7 +26502,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1204</v>
       </c>
@@ -25406,7 +26573,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1204</v>
       </c>
@@ -25477,7 +26644,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1204</v>
       </c>
@@ -25548,7 +26715,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1204</v>
       </c>
@@ -25619,7 +26786,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1204</v>
       </c>
@@ -25690,7 +26857,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1204</v>
       </c>
@@ -25761,7 +26928,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1204</v>
       </c>
@@ -25832,7 +26999,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1204</v>
       </c>
@@ -25903,14 +27070,14 @@
         <v>582</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1204</v>
       </c>
       <c r="B234">
         <v>6</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C234" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="D234">
@@ -25974,7 +27141,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1401</v>
       </c>
@@ -26039,7 +27206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1401</v>
       </c>
@@ -26110,7 +27277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1401</v>
       </c>
@@ -26175,7 +27342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1401</v>
       </c>
@@ -26240,7 +27407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1401</v>
       </c>
@@ -26305,7 +27472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1401</v>
       </c>
@@ -26376,7 +27543,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1401</v>
       </c>
@@ -26447,7 +27614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1401</v>
       </c>
@@ -26518,7 +27685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1401</v>
       </c>
@@ -26583,7 +27750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1401</v>
       </c>
@@ -26654,7 +27821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1401</v>
       </c>
@@ -26725,7 +27892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1401</v>
       </c>
@@ -26796,7 +27963,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1401</v>
       </c>
@@ -26867,7 +28034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1401</v>
       </c>
@@ -26938,7 +28105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1401</v>
       </c>
@@ -27003,7 +28170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1583</v>
       </c>
@@ -27071,7 +28238,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1583</v>
       </c>
@@ -27142,7 +28309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1583</v>
       </c>
@@ -27213,7 +28380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1583</v>
       </c>
@@ -27284,7 +28451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1583</v>
       </c>
@@ -27355,7 +28522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1583</v>
       </c>
@@ -27426,7 +28593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1583</v>
       </c>
@@ -27497,7 +28664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1583</v>
       </c>
@@ -27568,7 +28735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1679</v>
       </c>
@@ -27636,7 +28803,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1679</v>
       </c>
@@ -27704,7 +28871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1679</v>
       </c>
@@ -27772,7 +28939,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1679</v>
       </c>
@@ -27840,7 +29007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1679</v>
       </c>
@@ -27908,7 +29075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1679</v>
       </c>
@@ -27976,7 +29143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1679</v>
       </c>
@@ -28044,7 +29211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1679</v>
       </c>
@@ -28112,7 +29279,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1679</v>
       </c>
@@ -28180,7 +29347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1679</v>
       </c>
@@ -28248,7 +29415,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1790</v>
       </c>
@@ -28316,7 +29483,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1790</v>
       </c>
@@ -28384,7 +29551,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1790</v>
       </c>
@@ -28452,7 +29619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1790</v>
       </c>
@@ -28523,7 +29690,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1790</v>
       </c>
@@ -28594,7 +29761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1790</v>
       </c>
@@ -28665,7 +29832,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1790</v>
       </c>
@@ -28736,7 +29903,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1790</v>
       </c>
@@ -28807,7 +29974,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1790</v>
       </c>
@@ -28878,7 +30045,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1790</v>
       </c>
@@ -28949,7 +30116,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1790</v>
       </c>
@@ -29020,7 +30187,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1790</v>
       </c>
@@ -29091,7 +30258,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1790</v>
       </c>
@@ -29159,7 +30326,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1790</v>
       </c>
@@ -29227,7 +30394,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1790</v>
       </c>
@@ -29298,7 +30465,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1790</v>
       </c>
@@ -29366,7 +30533,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1790</v>
       </c>
@@ -29437,7 +30604,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1790</v>
       </c>
@@ -29505,7 +30672,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1790</v>
       </c>
@@ -29573,7 +30740,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1790</v>
       </c>
@@ -29641,7 +30808,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1790</v>
       </c>
@@ -29709,7 +30876,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1790</v>
       </c>
@@ -29777,7 +30944,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1790</v>
       </c>
@@ -29845,7 +31012,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1790</v>
       </c>
@@ -29913,7 +31080,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1790</v>
       </c>
@@ -29984,7 +31151,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1401</v>
       </c>
@@ -30055,7 +31222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1401</v>
       </c>
@@ -30126,7 +31293,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1401</v>
       </c>
@@ -30197,7 +31364,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1401</v>
       </c>
@@ -30262,7 +31429,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1401</v>
       </c>
@@ -30327,7 +31494,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1401</v>
       </c>
@@ -30392,7 +31559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1401</v>
       </c>
@@ -30457,7 +31624,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1401</v>
       </c>
@@ -30522,7 +31689,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1401</v>
       </c>
@@ -30587,7 +31754,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1401</v>
       </c>
@@ -30652,7 +31819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1401</v>
       </c>
@@ -30717,7 +31884,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1401</v>
       </c>
@@ -30782,7 +31949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1401</v>
       </c>
@@ -30847,7 +32014,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1401</v>
       </c>
@@ -30912,7 +32079,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1401</v>
       </c>
@@ -30977,7 +32144,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1401</v>
       </c>
@@ -31042,7 +32209,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1401</v>
       </c>
@@ -31107,7 +32274,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1401</v>
       </c>
@@ -31172,7 +32339,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1401</v>
       </c>
@@ -31237,7 +32404,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1401</v>
       </c>
@@ -31308,7 +32475,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1401</v>
       </c>
@@ -31373,7 +32540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1401</v>
       </c>
@@ -31438,7 +32605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1401</v>
       </c>
@@ -31503,7 +32670,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1401</v>
       </c>
@@ -31568,7 +32735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1401</v>
       </c>
@@ -31639,7 +32806,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1401</v>
       </c>
@@ -31704,7 +32871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>2380</v>
       </c>
@@ -31775,7 +32942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>2380</v>
       </c>
@@ -31846,7 +33013,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>2380</v>
       </c>
@@ -31917,7 +33084,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>2380</v>
       </c>
@@ -31988,7 +33155,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>2380</v>
       </c>
@@ -32059,7 +33226,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>2380</v>
       </c>
@@ -32130,7 +33297,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>2380</v>
       </c>
@@ -32195,7 +33362,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>2380</v>
       </c>
@@ -32266,7 +33433,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>2380</v>
       </c>
@@ -32337,7 +33504,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>2380</v>
       </c>
@@ -32408,7 +33575,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>2380</v>
       </c>
@@ -32473,7 +33640,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>2380</v>
       </c>
@@ -32544,7 +33711,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>2380</v>
       </c>
@@ -32615,7 +33782,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>2380</v>
       </c>
@@ -32686,7 +33853,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>2380</v>
       </c>
@@ -32751,7 +33918,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>2380</v>
       </c>
@@ -32822,7 +33989,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>2380</v>
       </c>
@@ -32890,7 +34057,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>2380</v>
       </c>
@@ -32961,7 +34128,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>2475</v>
       </c>
@@ -33032,7 +34199,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>2475</v>
       </c>
@@ -33103,7 +34270,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>2475</v>
       </c>
@@ -33174,7 +34341,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>2475</v>
       </c>
@@ -33245,7 +34412,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>2380</v>
       </c>
@@ -33316,7 +34483,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>2475</v>
       </c>
@@ -33387,7 +34554,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>2505</v>
       </c>
@@ -33458,7 +34625,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>2380</v>
       </c>
@@ -33529,7 +34696,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>2475</v>
       </c>
@@ -33600,7 +34767,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2475</v>
       </c>
@@ -33671,7 +34838,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>2380</v>
       </c>
@@ -33742,7 +34909,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>2380</v>
       </c>
@@ -33813,7 +34980,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2505</v>
       </c>
@@ -33884,7 +35051,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>2505</v>
       </c>
@@ -33955,7 +35122,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2505</v>
       </c>
@@ -34026,7 +35193,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>2475</v>
       </c>
@@ -34097,7 +35264,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>2505</v>
       </c>
@@ -34168,7 +35335,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2475</v>
       </c>
@@ -34239,7 +35406,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2475</v>
       </c>
@@ -34310,7 +35477,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2475</v>
       </c>
@@ -34381,7 +35548,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2475</v>
       </c>
@@ -34452,7 +35619,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>2475</v>
       </c>
@@ -34523,7 +35690,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>2475</v>
       </c>
@@ -34594,7 +35761,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>2475</v>
       </c>
@@ -34665,7 +35832,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>2475</v>
       </c>
@@ -34736,7 +35903,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>2475</v>
       </c>
@@ -34807,7 +35974,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>2475</v>
       </c>
@@ -34878,7 +36045,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>2475</v>
       </c>
@@ -34949,7 +36116,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>2475</v>
       </c>
@@ -35020,7 +36187,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>2505</v>
       </c>
@@ -35091,7 +36258,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>2475</v>
       </c>
@@ -35162,7 +36329,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>2505</v>
       </c>
@@ -35233,7 +36400,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>2475</v>
       </c>
@@ -35304,7 +36471,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>2505</v>
       </c>
@@ -35375,7 +36542,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>2475</v>
       </c>
@@ -35446,7 +36613,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>2505</v>
       </c>
@@ -35517,7 +36684,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>2505</v>
       </c>
@@ -35588,7 +36755,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>2475</v>
       </c>
@@ -35659,7 +36826,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>2677</v>
       </c>
@@ -35724,7 +36891,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>2677</v>
       </c>
@@ -35795,7 +36962,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>2677</v>
       </c>
@@ -35866,7 +37033,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>2677</v>
       </c>
@@ -35931,7 +37098,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2677</v>
       </c>
@@ -35996,7 +37163,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>2677</v>
       </c>
@@ -36058,7 +37225,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>2677</v>
       </c>
@@ -36123,7 +37290,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>2677</v>
       </c>
@@ -36188,7 +37355,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>2677</v>
       </c>
@@ -36253,7 +37420,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>2677</v>
       </c>
@@ -36318,7 +37485,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>2677</v>
       </c>
@@ -36383,7 +37550,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="386" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>2677</v>
       </c>
@@ -36448,7 +37615,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="387" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>2677</v>
       </c>
@@ -36513,7 +37680,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="388" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>2677</v>
       </c>
@@ -36578,7 +37745,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="389" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>2677</v>
       </c>
@@ -36643,7 +37810,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="390" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>2677</v>
       </c>
@@ -36708,7 +37875,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="391" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>2677</v>
       </c>
@@ -36773,7 +37940,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="392" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>2677</v>
       </c>
@@ -36844,7 +38011,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="393" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>2677</v>
       </c>
@@ -36909,7 +38076,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="394" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>2677</v>
       </c>
@@ -36980,7 +38147,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="395" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>2677</v>
       </c>
@@ -37045,7 +38212,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="396" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>2677</v>
       </c>
@@ -37110,7 +38277,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="397" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>2677</v>
       </c>
@@ -37172,7 +38339,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="398" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>2677</v>
       </c>
@@ -37237,7 +38404,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="399" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>2677</v>
       </c>
@@ -37302,7 +38469,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="400" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>2677</v>
       </c>
@@ -37367,7 +38534,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="401" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>2677</v>
       </c>
@@ -37432,7 +38599,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="402" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>2677</v>
       </c>
@@ -37497,7 +38664,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="403" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>2677</v>
       </c>
@@ -37562,7 +38729,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="404" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>2677</v>
       </c>
@@ -37627,7 +38794,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="405" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>2677</v>
       </c>
@@ -37692,7 +38859,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="406" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>2677</v>
       </c>
@@ -37757,7 +38924,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="407" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2677</v>
       </c>
@@ -37822,7 +38989,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="408" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>2677</v>
       </c>
@@ -37887,7 +39054,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="409" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>2677</v>
       </c>
@@ -37952,7 +39119,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="410" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>2677</v>
       </c>
@@ -38017,7 +39184,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="411" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>2677</v>
       </c>
@@ -38082,7 +39249,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="412" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>2677</v>
       </c>
@@ -38144,7 +39311,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="413" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>2677</v>
       </c>
@@ -38209,7 +39376,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="414" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>2677</v>
       </c>
@@ -38274,7 +39441,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="415" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>2677</v>
       </c>
@@ -38339,7 +39506,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="416" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>2677</v>
       </c>
@@ -38404,7 +39571,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="417" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>2677</v>
       </c>
@@ -38469,7 +39636,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="418" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>2677</v>
       </c>
@@ -38534,7 +39701,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="419" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>2677</v>
       </c>
@@ -38599,7 +39766,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="420" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>2677</v>
       </c>
@@ -38664,7 +39831,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="421" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>2677</v>
       </c>
@@ -38729,7 +39896,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="422" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>2677</v>
       </c>
@@ -38794,7 +39961,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="423" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>2677</v>
       </c>
@@ -38859,7 +40026,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="424" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>2677</v>
       </c>
@@ -38924,7 +40091,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="425" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>2677</v>
       </c>
@@ -38989,7 +40156,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="426" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>2677</v>
       </c>
@@ -39054,7 +40221,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="427" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>2677</v>
       </c>
@@ -39122,7 +40289,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="428" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>2677</v>
       </c>
@@ -39187,7 +40354,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="429" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>2677</v>
       </c>
@@ -39258,7 +40425,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="430" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>2677</v>
       </c>
@@ -39323,7 +40490,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="431" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>2677</v>
       </c>
@@ -39388,7 +40555,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="432" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>2677</v>
       </c>
@@ -39453,7 +40620,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="433" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>2677</v>
       </c>
@@ -39524,7 +40691,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="434" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>2677</v>
       </c>
@@ -39595,7 +40762,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="435" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>2677</v>
       </c>
@@ -39660,7 +40827,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="436" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>2677</v>
       </c>
@@ -39725,7 +40892,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="437" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>2677</v>
       </c>
@@ -39790,7 +40957,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="438" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>2677</v>
       </c>
@@ -39855,7 +41022,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="439" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>2677</v>
       </c>
@@ -39920,7 +41087,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="440" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>2677</v>
       </c>
@@ -39985,7 +41152,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="441" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>2677</v>
       </c>
@@ -40050,7 +41217,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="442" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>2677</v>
       </c>
@@ -40115,7 +41282,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="443" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>2677</v>
       </c>
@@ -40180,7 +41347,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="444" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>2677</v>
       </c>
@@ -40245,7 +41412,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="445" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>2677</v>
       </c>
@@ -40310,7 +41477,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="446" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>2677</v>
       </c>
@@ -40381,7 +41548,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="447" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>2677</v>
       </c>
@@ -40446,7 +41613,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="448" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>2677</v>
       </c>
@@ -40511,7 +41678,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="449" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>2677</v>
       </c>
@@ -40576,7 +41743,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="450" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>2677</v>
       </c>
@@ -40641,7 +41808,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="451" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>2677</v>
       </c>
@@ -40706,7 +41873,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="452" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>2677</v>
       </c>
@@ -40769,6 +41936,4479 @@
       </c>
       <c r="AA452">
         <v>270</v>
+      </c>
+    </row>
+    <row r="453" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B453">
+        <v>5</v>
+      </c>
+      <c r="C453" t="s">
+        <v>3147</v>
+      </c>
+      <c r="D453">
+        <v>-0.19819780000000001</v>
+      </c>
+      <c r="E453">
+        <v>-78.504957399999995</v>
+      </c>
+      <c r="F453">
+        <v>0</v>
+      </c>
+      <c r="G453">
+        <v>5</v>
+      </c>
+      <c r="H453" t="s">
+        <v>27</v>
+      </c>
+      <c r="I453" t="s">
+        <v>28</v>
+      </c>
+      <c r="J453">
+        <v>18.8</v>
+      </c>
+      <c r="M453" t="s">
+        <v>189</v>
+      </c>
+      <c r="N453" t="s">
+        <v>1378</v>
+      </c>
+      <c r="O453" t="s">
+        <v>3148</v>
+      </c>
+      <c r="P453" s="6" t="s">
+        <v>3149</v>
+      </c>
+      <c r="Q453">
+        <v>759534061</v>
+      </c>
+      <c r="R453" t="s">
+        <v>3150</v>
+      </c>
+      <c r="S453" s="1">
+        <v>46163.96702546296</v>
+      </c>
+      <c r="V453" t="s">
+        <v>29</v>
+      </c>
+      <c r="X453" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z453" t="s">
+        <v>3151</v>
+      </c>
+      <c r="AA453">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="454" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B454">
+        <v>5</v>
+      </c>
+      <c r="C454" t="s">
+        <v>3152</v>
+      </c>
+      <c r="D454">
+        <v>-0.19866510000000001</v>
+      </c>
+      <c r="E454">
+        <v>-78.504593999999997</v>
+      </c>
+      <c r="F454">
+        <v>0</v>
+      </c>
+      <c r="G454">
+        <v>5</v>
+      </c>
+      <c r="H454" t="s">
+        <v>27</v>
+      </c>
+      <c r="I454" t="s">
+        <v>60</v>
+      </c>
+      <c r="J454">
+        <v>20.6</v>
+      </c>
+      <c r="K454">
+        <v>17</v>
+      </c>
+      <c r="L454" t="s">
+        <v>874</v>
+      </c>
+      <c r="M454" t="s">
+        <v>187</v>
+      </c>
+      <c r="N454" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O454" t="s">
+        <v>3153</v>
+      </c>
+      <c r="P454" s="6" t="s">
+        <v>3154</v>
+      </c>
+      <c r="Q454">
+        <v>759537413</v>
+      </c>
+      <c r="R454" t="s">
+        <v>3155</v>
+      </c>
+      <c r="S454" s="1">
+        <v>46163.979456018518</v>
+      </c>
+      <c r="V454" t="s">
+        <v>29</v>
+      </c>
+      <c r="X454" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z454" t="s">
+        <v>3156</v>
+      </c>
+      <c r="AA454">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="455" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B455">
+        <v>5</v>
+      </c>
+      <c r="C455" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D455">
+        <v>-0.19866909999999999</v>
+      </c>
+      <c r="E455">
+        <v>-78.504834700000004</v>
+      </c>
+      <c r="F455">
+        <v>0</v>
+      </c>
+      <c r="G455">
+        <v>5</v>
+      </c>
+      <c r="H455" t="s">
+        <v>27</v>
+      </c>
+      <c r="I455" t="s">
+        <v>28</v>
+      </c>
+      <c r="J455">
+        <v>20.6</v>
+      </c>
+      <c r="K455">
+        <v>19</v>
+      </c>
+      <c r="L455" t="s">
+        <v>874</v>
+      </c>
+      <c r="M455" t="s">
+        <v>187</v>
+      </c>
+      <c r="N455" t="s">
+        <v>1396</v>
+      </c>
+      <c r="O455" t="s">
+        <v>3158</v>
+      </c>
+      <c r="P455" s="6" t="s">
+        <v>3159</v>
+      </c>
+      <c r="Q455">
+        <v>759537486</v>
+      </c>
+      <c r="R455" t="s">
+        <v>3160</v>
+      </c>
+      <c r="S455" s="1">
+        <v>46163.979722222219</v>
+      </c>
+      <c r="V455" t="s">
+        <v>29</v>
+      </c>
+      <c r="X455" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z455" t="s">
+        <v>3161</v>
+      </c>
+      <c r="AA455">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="456" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B456">
+        <v>5</v>
+      </c>
+      <c r="C456" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D456">
+        <v>-0.1986185</v>
+      </c>
+      <c r="E456">
+        <v>-78.505029800000003</v>
+      </c>
+      <c r="F456">
+        <v>0</v>
+      </c>
+      <c r="G456">
+        <v>5</v>
+      </c>
+      <c r="H456" t="s">
+        <v>27</v>
+      </c>
+      <c r="I456" t="s">
+        <v>60</v>
+      </c>
+      <c r="J456">
+        <v>19.2</v>
+      </c>
+      <c r="K456">
+        <v>2</v>
+      </c>
+      <c r="L456" t="s">
+        <v>874</v>
+      </c>
+      <c r="M456" t="s">
+        <v>187</v>
+      </c>
+      <c r="N456" t="s">
+        <v>1390</v>
+      </c>
+      <c r="O456" t="s">
+        <v>3163</v>
+      </c>
+      <c r="P456" s="6" t="s">
+        <v>3164</v>
+      </c>
+      <c r="Q456">
+        <v>759537661</v>
+      </c>
+      <c r="R456" t="s">
+        <v>3165</v>
+      </c>
+      <c r="S456" s="1">
+        <v>46163.98027777778</v>
+      </c>
+      <c r="V456" t="s">
+        <v>29</v>
+      </c>
+      <c r="X456" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z456" t="s">
+        <v>3166</v>
+      </c>
+      <c r="AA456">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="457" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B457">
+        <v>5</v>
+      </c>
+      <c r="C457" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D457">
+        <v>-0.1984331</v>
+      </c>
+      <c r="E457">
+        <v>-78.505006699999996</v>
+      </c>
+      <c r="F457">
+        <v>0</v>
+      </c>
+      <c r="G457">
+        <v>5</v>
+      </c>
+      <c r="H457" t="s">
+        <v>27</v>
+      </c>
+      <c r="I457" t="s">
+        <v>28</v>
+      </c>
+      <c r="J457">
+        <v>19.2</v>
+      </c>
+      <c r="K457">
+        <v>23</v>
+      </c>
+      <c r="L457" t="s">
+        <v>874</v>
+      </c>
+      <c r="M457" t="s">
+        <v>187</v>
+      </c>
+      <c r="N457" t="s">
+        <v>1384</v>
+      </c>
+      <c r="O457" t="s">
+        <v>3168</v>
+      </c>
+      <c r="P457" s="6" t="s">
+        <v>3169</v>
+      </c>
+      <c r="Q457">
+        <v>759537759</v>
+      </c>
+      <c r="R457" t="s">
+        <v>3170</v>
+      </c>
+      <c r="S457" s="1">
+        <v>46163.980682870373</v>
+      </c>
+      <c r="V457" t="s">
+        <v>29</v>
+      </c>
+      <c r="X457" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z457" t="s">
+        <v>3171</v>
+      </c>
+      <c r="AA457">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="458" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B458">
+        <v>5</v>
+      </c>
+      <c r="C458" t="s">
+        <v>3172</v>
+      </c>
+      <c r="D458">
+        <v>-0.19802939999999999</v>
+      </c>
+      <c r="E458">
+        <v>-78.504889700000007</v>
+      </c>
+      <c r="F458">
+        <v>0</v>
+      </c>
+      <c r="G458">
+        <v>5</v>
+      </c>
+      <c r="H458" t="s">
+        <v>27</v>
+      </c>
+      <c r="I458" t="s">
+        <v>60</v>
+      </c>
+      <c r="J458">
+        <v>18.8</v>
+      </c>
+      <c r="K458">
+        <v>23</v>
+      </c>
+      <c r="L458" t="s">
+        <v>874</v>
+      </c>
+      <c r="M458" t="s">
+        <v>187</v>
+      </c>
+      <c r="N458" t="s">
+        <v>1372</v>
+      </c>
+      <c r="O458" t="s">
+        <v>3173</v>
+      </c>
+      <c r="P458" s="6" t="s">
+        <v>3174</v>
+      </c>
+      <c r="Q458">
+        <v>759538587</v>
+      </c>
+      <c r="R458" t="s">
+        <v>3175</v>
+      </c>
+      <c r="S458" s="1">
+        <v>46163.983888888892</v>
+      </c>
+      <c r="V458" t="s">
+        <v>29</v>
+      </c>
+      <c r="X458" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z458" t="s">
+        <v>3176</v>
+      </c>
+      <c r="AA458">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="459" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B459">
+        <v>5</v>
+      </c>
+      <c r="C459" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D459">
+        <v>-0.19794030000000001</v>
+      </c>
+      <c r="E459">
+        <v>-78.504918900000007</v>
+      </c>
+      <c r="F459">
+        <v>0</v>
+      </c>
+      <c r="G459">
+        <v>5</v>
+      </c>
+      <c r="H459" t="s">
+        <v>27</v>
+      </c>
+      <c r="I459" t="s">
+        <v>60</v>
+      </c>
+      <c r="J459">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K459">
+        <v>29</v>
+      </c>
+      <c r="L459" t="s">
+        <v>874</v>
+      </c>
+      <c r="M459" t="s">
+        <v>187</v>
+      </c>
+      <c r="N459" t="s">
+        <v>3178</v>
+      </c>
+      <c r="O459" t="s">
+        <v>3179</v>
+      </c>
+      <c r="P459" s="6" t="s">
+        <v>3180</v>
+      </c>
+      <c r="Q459">
+        <v>759538754</v>
+      </c>
+      <c r="R459" t="s">
+        <v>3181</v>
+      </c>
+      <c r="S459" s="1">
+        <v>46163.984618055547</v>
+      </c>
+      <c r="V459" t="s">
+        <v>29</v>
+      </c>
+      <c r="X459" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z459" t="s">
+        <v>3182</v>
+      </c>
+      <c r="AA459">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="460" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B460">
+        <v>5</v>
+      </c>
+      <c r="C460" t="s">
+        <v>3183</v>
+      </c>
+      <c r="D460">
+        <v>-0.1976291</v>
+      </c>
+      <c r="E460">
+        <v>-78.504895000000005</v>
+      </c>
+      <c r="F460">
+        <v>0</v>
+      </c>
+      <c r="G460">
+        <v>5</v>
+      </c>
+      <c r="H460" t="s">
+        <v>27</v>
+      </c>
+      <c r="I460" t="s">
+        <v>60</v>
+      </c>
+      <c r="J460">
+        <v>19.2</v>
+      </c>
+      <c r="K460">
+        <v>26</v>
+      </c>
+      <c r="L460" t="s">
+        <v>874</v>
+      </c>
+      <c r="M460" t="s">
+        <v>187</v>
+      </c>
+      <c r="N460" t="s">
+        <v>1366</v>
+      </c>
+      <c r="O460" t="s">
+        <v>3184</v>
+      </c>
+      <c r="P460" s="6" t="s">
+        <v>3185</v>
+      </c>
+      <c r="Q460">
+        <v>759538891</v>
+      </c>
+      <c r="R460" t="s">
+        <v>3186</v>
+      </c>
+      <c r="S460" s="1">
+        <v>46163.985254629632</v>
+      </c>
+      <c r="V460" t="s">
+        <v>29</v>
+      </c>
+      <c r="X460" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z460" t="s">
+        <v>3187</v>
+      </c>
+      <c r="AA460">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="461" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B461">
+        <v>5</v>
+      </c>
+      <c r="C461" t="s">
+        <v>3188</v>
+      </c>
+      <c r="D461">
+        <v>-0.1972932</v>
+      </c>
+      <c r="E461">
+        <v>-78.504455500000006</v>
+      </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
+      <c r="G461">
+        <v>5</v>
+      </c>
+      <c r="H461" t="s">
+        <v>33</v>
+      </c>
+      <c r="I461" t="s">
+        <v>60</v>
+      </c>
+      <c r="J461">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M461" t="s">
+        <v>189</v>
+      </c>
+      <c r="N461" t="s">
+        <v>1360</v>
+      </c>
+      <c r="O461" t="s">
+        <v>3189</v>
+      </c>
+      <c r="P461" s="6" t="s">
+        <v>3190</v>
+      </c>
+      <c r="Q461">
+        <v>759538970</v>
+      </c>
+      <c r="R461" t="s">
+        <v>3191</v>
+      </c>
+      <c r="S461" s="1">
+        <v>46163.985671296286</v>
+      </c>
+      <c r="V461" t="s">
+        <v>29</v>
+      </c>
+      <c r="X461" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z461" t="s">
+        <v>3192</v>
+      </c>
+      <c r="AA461">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="462" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B462">
+        <v>5</v>
+      </c>
+      <c r="C462" t="s">
+        <v>3193</v>
+      </c>
+      <c r="D462">
+        <v>-0.1972999</v>
+      </c>
+      <c r="E462">
+        <v>-78.504454499999994</v>
+      </c>
+      <c r="F462">
+        <v>0</v>
+      </c>
+      <c r="G462">
+        <v>5</v>
+      </c>
+      <c r="H462" t="s">
+        <v>33</v>
+      </c>
+      <c r="I462" t="s">
+        <v>60</v>
+      </c>
+      <c r="J462">
+        <v>7.88</v>
+      </c>
+      <c r="M462" t="s">
+        <v>189</v>
+      </c>
+      <c r="N462" t="s">
+        <v>1354</v>
+      </c>
+      <c r="O462" t="s">
+        <v>3194</v>
+      </c>
+      <c r="P462" s="6" t="s">
+        <v>3195</v>
+      </c>
+      <c r="Q462">
+        <v>759539287</v>
+      </c>
+      <c r="R462" t="s">
+        <v>3196</v>
+      </c>
+      <c r="S462" s="1">
+        <v>46163.987222222233</v>
+      </c>
+      <c r="V462" t="s">
+        <v>29</v>
+      </c>
+      <c r="X462" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z462" t="s">
+        <v>3197</v>
+      </c>
+      <c r="AA462">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="463" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B463">
+        <v>5</v>
+      </c>
+      <c r="C463" t="s">
+        <v>3198</v>
+      </c>
+      <c r="D463">
+        <v>-0.19773209999999999</v>
+      </c>
+      <c r="E463">
+        <v>-78.504787800000003</v>
+      </c>
+      <c r="F463">
+        <v>0</v>
+      </c>
+      <c r="G463">
+        <v>4</v>
+      </c>
+      <c r="H463" t="s">
+        <v>27</v>
+      </c>
+      <c r="I463" t="s">
+        <v>60</v>
+      </c>
+      <c r="J463">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K463">
+        <v>23</v>
+      </c>
+      <c r="L463" t="s">
+        <v>874</v>
+      </c>
+      <c r="M463" t="s">
+        <v>187</v>
+      </c>
+      <c r="N463" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O463" t="s">
+        <v>3199</v>
+      </c>
+      <c r="P463" s="6" t="s">
+        <v>3200</v>
+      </c>
+      <c r="Q463">
+        <v>759539760</v>
+      </c>
+      <c r="R463" t="s">
+        <v>3201</v>
+      </c>
+      <c r="S463" s="1">
+        <v>46163.989502314813</v>
+      </c>
+      <c r="V463" t="s">
+        <v>29</v>
+      </c>
+      <c r="X463" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z463" t="s">
+        <v>3202</v>
+      </c>
+      <c r="AA463">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="464" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>3146</v>
+      </c>
+      <c r="B464">
+        <v>5</v>
+      </c>
+      <c r="C464" t="s">
+        <v>3203</v>
+      </c>
+      <c r="D464">
+        <v>-0.19813710000000001</v>
+      </c>
+      <c r="E464">
+        <v>-78.504760599999997</v>
+      </c>
+      <c r="F464">
+        <v>0</v>
+      </c>
+      <c r="G464">
+        <v>4</v>
+      </c>
+      <c r="H464" t="s">
+        <v>27</v>
+      </c>
+      <c r="I464" t="s">
+        <v>28</v>
+      </c>
+      <c r="J464">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M464" t="s">
+        <v>189</v>
+      </c>
+      <c r="N464" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O464" t="s">
+        <v>3204</v>
+      </c>
+      <c r="P464" s="6" t="s">
+        <v>3205</v>
+      </c>
+      <c r="Q464">
+        <v>759540023</v>
+      </c>
+      <c r="R464" t="s">
+        <v>3206</v>
+      </c>
+      <c r="S464" s="1">
+        <v>46163.990497685183</v>
+      </c>
+      <c r="V464" t="s">
+        <v>29</v>
+      </c>
+      <c r="X464" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z464" t="s">
+        <v>3207</v>
+      </c>
+      <c r="AA464">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="465" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B465">
+        <v>5</v>
+      </c>
+      <c r="C465" t="s">
+        <v>3209</v>
+      </c>
+      <c r="D465">
+        <v>-0.19750210000000001</v>
+      </c>
+      <c r="E465">
+        <v>-78.505021400000004</v>
+      </c>
+      <c r="F465">
+        <v>0</v>
+      </c>
+      <c r="G465">
+        <v>5</v>
+      </c>
+      <c r="H465" t="s">
+        <v>33</v>
+      </c>
+      <c r="I465" t="s">
+        <v>28</v>
+      </c>
+      <c r="J465">
+        <v>10.45</v>
+      </c>
+      <c r="K465">
+        <v>68</v>
+      </c>
+      <c r="L465" t="s">
+        <v>874</v>
+      </c>
+      <c r="M465" t="s">
+        <v>187</v>
+      </c>
+      <c r="N465" t="s">
+        <v>3210</v>
+      </c>
+      <c r="O465" t="s">
+        <v>3211</v>
+      </c>
+      <c r="P465" s="6" t="s">
+        <v>3212</v>
+      </c>
+      <c r="Q465">
+        <v>759541471</v>
+      </c>
+      <c r="R465" t="s">
+        <v>3213</v>
+      </c>
+      <c r="S465" s="1">
+        <v>46163.995312500003</v>
+      </c>
+      <c r="V465" t="s">
+        <v>29</v>
+      </c>
+      <c r="X465" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z465" t="s">
+        <v>3214</v>
+      </c>
+      <c r="AA465">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="466" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B466">
+        <v>5</v>
+      </c>
+      <c r="C466" t="s">
+        <v>3215</v>
+      </c>
+      <c r="D466">
+        <v>-0.19771630000000001</v>
+      </c>
+      <c r="E466">
+        <v>-78.505419399999994</v>
+      </c>
+      <c r="F466">
+        <v>0</v>
+      </c>
+      <c r="G466">
+        <v>5</v>
+      </c>
+      <c r="H466" t="s">
+        <v>33</v>
+      </c>
+      <c r="I466" t="s">
+        <v>28</v>
+      </c>
+      <c r="J466">
+        <v>10.45</v>
+      </c>
+      <c r="K466">
+        <v>60</v>
+      </c>
+      <c r="L466" t="s">
+        <v>874</v>
+      </c>
+      <c r="M466" t="s">
+        <v>187</v>
+      </c>
+      <c r="N466" t="s">
+        <v>3216</v>
+      </c>
+      <c r="O466" t="s">
+        <v>3217</v>
+      </c>
+      <c r="P466" s="6" t="s">
+        <v>3218</v>
+      </c>
+      <c r="Q466">
+        <v>759542176</v>
+      </c>
+      <c r="R466" t="s">
+        <v>3219</v>
+      </c>
+      <c r="S466" s="1">
+        <v>46163.997488425928</v>
+      </c>
+      <c r="V466" t="s">
+        <v>29</v>
+      </c>
+      <c r="X466" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z466" t="s">
+        <v>3220</v>
+      </c>
+      <c r="AA466">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="467" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B467">
+        <v>5</v>
+      </c>
+      <c r="C467" t="s">
+        <v>3221</v>
+      </c>
+      <c r="D467">
+        <v>-0.19785140000000001</v>
+      </c>
+      <c r="E467">
+        <v>-78.505704399999999</v>
+      </c>
+      <c r="F467">
+        <v>0</v>
+      </c>
+      <c r="G467">
+        <v>5</v>
+      </c>
+      <c r="H467" t="s">
+        <v>33</v>
+      </c>
+      <c r="I467" t="s">
+        <v>28</v>
+      </c>
+      <c r="J467">
+        <v>10.5</v>
+      </c>
+      <c r="K467">
+        <v>61</v>
+      </c>
+      <c r="L467" t="s">
+        <v>874</v>
+      </c>
+      <c r="M467" t="s">
+        <v>187</v>
+      </c>
+      <c r="N467" t="s">
+        <v>3222</v>
+      </c>
+      <c r="O467" t="s">
+        <v>3223</v>
+      </c>
+      <c r="P467" s="6" t="s">
+        <v>3224</v>
+      </c>
+      <c r="Q467">
+        <v>759543234</v>
+      </c>
+      <c r="R467" t="s">
+        <v>3225</v>
+      </c>
+      <c r="S467" s="1">
+        <v>46164.001597222217</v>
+      </c>
+      <c r="V467" t="s">
+        <v>29</v>
+      </c>
+      <c r="X467" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z467" t="s">
+        <v>3226</v>
+      </c>
+      <c r="AA467">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="468" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B468">
+        <v>5</v>
+      </c>
+      <c r="C468" t="s">
+        <v>3227</v>
+      </c>
+      <c r="D468">
+        <v>-0.19805890000000001</v>
+      </c>
+      <c r="E468">
+        <v>-78.505935100000002</v>
+      </c>
+      <c r="F468">
+        <v>0</v>
+      </c>
+      <c r="G468">
+        <v>5</v>
+      </c>
+      <c r="H468" t="s">
+        <v>33</v>
+      </c>
+      <c r="I468" t="s">
+        <v>28</v>
+      </c>
+      <c r="J468">
+        <v>11.5</v>
+      </c>
+      <c r="K468">
+        <v>43</v>
+      </c>
+      <c r="L468" t="s">
+        <v>874</v>
+      </c>
+      <c r="M468" t="s">
+        <v>187</v>
+      </c>
+      <c r="N468" t="s">
+        <v>3228</v>
+      </c>
+      <c r="O468" t="s">
+        <v>3229</v>
+      </c>
+      <c r="P468" s="6" t="s">
+        <v>3230</v>
+      </c>
+      <c r="Q468">
+        <v>759544055</v>
+      </c>
+      <c r="R468" t="s">
+        <v>3231</v>
+      </c>
+      <c r="S468" s="1">
+        <v>46164.004826388889</v>
+      </c>
+      <c r="V468" t="s">
+        <v>29</v>
+      </c>
+      <c r="X468" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z468" t="s">
+        <v>3232</v>
+      </c>
+      <c r="AA468">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="469" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B469">
+        <v>5</v>
+      </c>
+      <c r="C469" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D469">
+        <v>-0.198076</v>
+      </c>
+      <c r="E469">
+        <v>-78.505927</v>
+      </c>
+      <c r="F469">
+        <v>0</v>
+      </c>
+      <c r="G469">
+        <v>5</v>
+      </c>
+      <c r="H469" t="s">
+        <v>33</v>
+      </c>
+      <c r="I469" t="s">
+        <v>28</v>
+      </c>
+      <c r="J469">
+        <v>11.5</v>
+      </c>
+      <c r="K469">
+        <v>106</v>
+      </c>
+      <c r="L469" t="s">
+        <v>874</v>
+      </c>
+      <c r="M469" t="s">
+        <v>187</v>
+      </c>
+      <c r="N469" t="s">
+        <v>3234</v>
+      </c>
+      <c r="O469" t="s">
+        <v>3235</v>
+      </c>
+      <c r="P469" s="6" t="s">
+        <v>3236</v>
+      </c>
+      <c r="Q469">
+        <v>759544554</v>
+      </c>
+      <c r="R469" t="s">
+        <v>3237</v>
+      </c>
+      <c r="S469" s="1">
+        <v>46164.006331018521</v>
+      </c>
+      <c r="V469" t="s">
+        <v>29</v>
+      </c>
+      <c r="X469" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z469" t="s">
+        <v>3238</v>
+      </c>
+      <c r="AA469">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="470" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B470">
+        <v>5</v>
+      </c>
+      <c r="C470" t="s">
+        <v>3239</v>
+      </c>
+      <c r="D470">
+        <v>-0.1979919</v>
+      </c>
+      <c r="E470">
+        <v>-78.505701400000007</v>
+      </c>
+      <c r="F470">
+        <v>0</v>
+      </c>
+      <c r="G470">
+        <v>5</v>
+      </c>
+      <c r="H470" t="s">
+        <v>27</v>
+      </c>
+      <c r="I470" t="s">
+        <v>28</v>
+      </c>
+      <c r="J470">
+        <v>13.54</v>
+      </c>
+      <c r="M470" t="s">
+        <v>189</v>
+      </c>
+      <c r="N470" t="s">
+        <v>3240</v>
+      </c>
+      <c r="O470" t="s">
+        <v>3241</v>
+      </c>
+      <c r="P470" s="6" t="s">
+        <v>3242</v>
+      </c>
+      <c r="Q470">
+        <v>759545341</v>
+      </c>
+      <c r="R470" t="s">
+        <v>3243</v>
+      </c>
+      <c r="S470" s="1">
+        <v>46164.009027777778</v>
+      </c>
+      <c r="V470" t="s">
+        <v>29</v>
+      </c>
+      <c r="X470" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z470" t="s">
+        <v>3244</v>
+      </c>
+      <c r="AA470">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="471" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B471">
+        <v>5</v>
+      </c>
+      <c r="C471" t="s">
+        <v>3245</v>
+      </c>
+      <c r="D471">
+        <v>-0.19816990000000001</v>
+      </c>
+      <c r="E471">
+        <v>-78.505726199999998</v>
+      </c>
+      <c r="F471">
+        <v>0</v>
+      </c>
+      <c r="G471">
+        <v>5</v>
+      </c>
+      <c r="H471" t="s">
+        <v>27</v>
+      </c>
+      <c r="I471" t="s">
+        <v>60</v>
+      </c>
+      <c r="J471">
+        <v>13.54</v>
+      </c>
+      <c r="M471" t="s">
+        <v>189</v>
+      </c>
+      <c r="N471" t="s">
+        <v>3246</v>
+      </c>
+      <c r="O471" t="s">
+        <v>3247</v>
+      </c>
+      <c r="P471" s="6" t="s">
+        <v>3248</v>
+      </c>
+      <c r="Q471">
+        <v>759545629</v>
+      </c>
+      <c r="R471" t="s">
+        <v>3249</v>
+      </c>
+      <c r="S471" s="1">
+        <v>46164.010023148148</v>
+      </c>
+      <c r="V471" t="s">
+        <v>29</v>
+      </c>
+      <c r="X471" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z471" t="s">
+        <v>3250</v>
+      </c>
+      <c r="AA471">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="472" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B472">
+        <v>5</v>
+      </c>
+      <c r="C472" t="s">
+        <v>3251</v>
+      </c>
+      <c r="D472">
+        <v>-0.1981522</v>
+      </c>
+      <c r="E472">
+        <v>-78.505628999999999</v>
+      </c>
+      <c r="F472">
+        <v>0</v>
+      </c>
+      <c r="G472">
+        <v>5</v>
+      </c>
+      <c r="H472" t="s">
+        <v>27</v>
+      </c>
+      <c r="I472" t="s">
+        <v>28</v>
+      </c>
+      <c r="J472">
+        <v>9.32</v>
+      </c>
+      <c r="M472" t="s">
+        <v>189</v>
+      </c>
+      <c r="N472" t="s">
+        <v>3252</v>
+      </c>
+      <c r="O472" t="s">
+        <v>3253</v>
+      </c>
+      <c r="P472" s="6" t="s">
+        <v>3254</v>
+      </c>
+      <c r="Q472">
+        <v>759545955</v>
+      </c>
+      <c r="R472" t="s">
+        <v>3255</v>
+      </c>
+      <c r="S472" s="1">
+        <v>46164.010879629634</v>
+      </c>
+      <c r="V472" t="s">
+        <v>29</v>
+      </c>
+      <c r="X472" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z472" t="s">
+        <v>3256</v>
+      </c>
+      <c r="AA472">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="473" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B473">
+        <v>5</v>
+      </c>
+      <c r="C473" t="s">
+        <v>3257</v>
+      </c>
+      <c r="D473">
+        <v>-0.19826779999999999</v>
+      </c>
+      <c r="E473">
+        <v>-78.505868000000007</v>
+      </c>
+      <c r="F473">
+        <v>0</v>
+      </c>
+      <c r="G473">
+        <v>5</v>
+      </c>
+      <c r="H473" t="s">
+        <v>33</v>
+      </c>
+      <c r="I473" t="s">
+        <v>28</v>
+      </c>
+      <c r="J473">
+        <v>9.73</v>
+      </c>
+      <c r="M473" t="s">
+        <v>189</v>
+      </c>
+      <c r="N473" t="s">
+        <v>3258</v>
+      </c>
+      <c r="O473" t="s">
+        <v>3259</v>
+      </c>
+      <c r="P473" s="6" t="s">
+        <v>3260</v>
+      </c>
+      <c r="Q473">
+        <v>759546516</v>
+      </c>
+      <c r="R473" t="s">
+        <v>3261</v>
+      </c>
+      <c r="S473" s="1">
+        <v>46164.013425925928</v>
+      </c>
+      <c r="V473" t="s">
+        <v>29</v>
+      </c>
+      <c r="X473" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z473" t="s">
+        <v>3262</v>
+      </c>
+      <c r="AA473">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="474" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B474">
+        <v>5</v>
+      </c>
+      <c r="C474" t="s">
+        <v>3263</v>
+      </c>
+      <c r="D474">
+        <v>-0.19826279999999999</v>
+      </c>
+      <c r="E474">
+        <v>-78.505893200000003</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474">
+        <v>5</v>
+      </c>
+      <c r="H474" t="s">
+        <v>33</v>
+      </c>
+      <c r="I474" t="s">
+        <v>28</v>
+      </c>
+      <c r="J474">
+        <v>9.73</v>
+      </c>
+      <c r="M474" t="s">
+        <v>189</v>
+      </c>
+      <c r="N474" t="s">
+        <v>3264</v>
+      </c>
+      <c r="O474" t="s">
+        <v>3265</v>
+      </c>
+      <c r="P474" s="6" t="s">
+        <v>3266</v>
+      </c>
+      <c r="Q474">
+        <v>759546712</v>
+      </c>
+      <c r="R474" t="s">
+        <v>3267</v>
+      </c>
+      <c r="S474" s="1">
+        <v>46164.014351851853</v>
+      </c>
+      <c r="V474" t="s">
+        <v>29</v>
+      </c>
+      <c r="X474" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z474" t="s">
+        <v>3268</v>
+      </c>
+      <c r="AA474">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="475" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B475">
+        <v>5</v>
+      </c>
+      <c r="C475" t="s">
+        <v>3269</v>
+      </c>
+      <c r="D475">
+        <v>-0.19849649999999999</v>
+      </c>
+      <c r="E475">
+        <v>-78.505572650000005</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475">
+        <v>5</v>
+      </c>
+      <c r="H475" t="s">
+        <v>33</v>
+      </c>
+      <c r="I475" t="s">
+        <v>28</v>
+      </c>
+      <c r="J475">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="M475" t="s">
+        <v>189</v>
+      </c>
+      <c r="N475" t="s">
+        <v>3270</v>
+      </c>
+      <c r="O475" t="s">
+        <v>3271</v>
+      </c>
+      <c r="P475" s="6" t="s">
+        <v>3272</v>
+      </c>
+      <c r="Q475">
+        <v>759547482</v>
+      </c>
+      <c r="R475" t="s">
+        <v>3273</v>
+      </c>
+      <c r="S475" s="1">
+        <v>46164.01761574074</v>
+      </c>
+      <c r="V475" t="s">
+        <v>29</v>
+      </c>
+      <c r="X475" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z475" t="s">
+        <v>3274</v>
+      </c>
+      <c r="AA475">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="476" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B476">
+        <v>5</v>
+      </c>
+      <c r="C476" t="s">
+        <v>3275</v>
+      </c>
+      <c r="D476">
+        <v>-0.19855143</v>
+      </c>
+      <c r="E476">
+        <v>-78.505720499999995</v>
+      </c>
+      <c r="F476">
+        <v>0</v>
+      </c>
+      <c r="G476">
+        <v>5</v>
+      </c>
+      <c r="H476" t="s">
+        <v>33</v>
+      </c>
+      <c r="I476" t="s">
+        <v>28</v>
+      </c>
+      <c r="J476">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="M476" t="s">
+        <v>189</v>
+      </c>
+      <c r="N476" t="s">
+        <v>3276</v>
+      </c>
+      <c r="O476" t="s">
+        <v>3277</v>
+      </c>
+      <c r="P476" s="6" t="s">
+        <v>3278</v>
+      </c>
+      <c r="Q476">
+        <v>759547992</v>
+      </c>
+      <c r="R476" t="s">
+        <v>3279</v>
+      </c>
+      <c r="S476" s="1">
+        <v>46164.01898148148</v>
+      </c>
+      <c r="V476" t="s">
+        <v>29</v>
+      </c>
+      <c r="X476" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z476" t="s">
+        <v>3280</v>
+      </c>
+      <c r="AA476">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="477" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B477">
+        <v>5</v>
+      </c>
+      <c r="C477" t="s">
+        <v>3281</v>
+      </c>
+      <c r="D477">
+        <v>-0.1984918</v>
+      </c>
+      <c r="E477">
+        <v>-78.505724200000003</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
+      <c r="G477">
+        <v>5</v>
+      </c>
+      <c r="H477" t="s">
+        <v>33</v>
+      </c>
+      <c r="I477" t="s">
+        <v>28</v>
+      </c>
+      <c r="J477">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="M477" t="s">
+        <v>189</v>
+      </c>
+      <c r="N477" t="s">
+        <v>3282</v>
+      </c>
+      <c r="O477" t="s">
+        <v>3283</v>
+      </c>
+      <c r="P477" s="6" t="s">
+        <v>3284</v>
+      </c>
+      <c r="Q477">
+        <v>759548230</v>
+      </c>
+      <c r="R477" t="s">
+        <v>3285</v>
+      </c>
+      <c r="S477" s="1">
+        <v>46164.019687499997</v>
+      </c>
+      <c r="V477" t="s">
+        <v>29</v>
+      </c>
+      <c r="X477" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z477" t="s">
+        <v>3286</v>
+      </c>
+      <c r="AA477">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="478" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B478">
+        <v>5</v>
+      </c>
+      <c r="C478" t="s">
+        <v>3287</v>
+      </c>
+      <c r="D478">
+        <v>-0.19851959999999999</v>
+      </c>
+      <c r="E478">
+        <v>-78.505579699999998</v>
+      </c>
+      <c r="F478">
+        <v>0</v>
+      </c>
+      <c r="G478">
+        <v>5</v>
+      </c>
+      <c r="H478" t="s">
+        <v>27</v>
+      </c>
+      <c r="I478" t="s">
+        <v>28</v>
+      </c>
+      <c r="J478">
+        <v>13.12</v>
+      </c>
+      <c r="M478" t="s">
+        <v>189</v>
+      </c>
+      <c r="N478" t="s">
+        <v>3288</v>
+      </c>
+      <c r="O478" t="s">
+        <v>3289</v>
+      </c>
+      <c r="P478" s="6" t="s">
+        <v>3290</v>
+      </c>
+      <c r="Q478">
+        <v>759549783</v>
+      </c>
+      <c r="R478" t="s">
+        <v>3291</v>
+      </c>
+      <c r="S478" s="1">
+        <v>46164.02548611111</v>
+      </c>
+      <c r="V478" t="s">
+        <v>29</v>
+      </c>
+      <c r="X478" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z478" t="s">
+        <v>3292</v>
+      </c>
+      <c r="AA478">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="479" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B479">
+        <v>5</v>
+      </c>
+      <c r="C479" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D479">
+        <v>-0.19852059999999999</v>
+      </c>
+      <c r="E479">
+        <v>-78.505553500000005</v>
+      </c>
+      <c r="F479">
+        <v>0</v>
+      </c>
+      <c r="G479">
+        <v>5</v>
+      </c>
+      <c r="H479" t="s">
+        <v>27</v>
+      </c>
+      <c r="I479" t="s">
+        <v>28</v>
+      </c>
+      <c r="J479">
+        <v>8.5</v>
+      </c>
+      <c r="M479" t="s">
+        <v>189</v>
+      </c>
+      <c r="N479" t="s">
+        <v>3294</v>
+      </c>
+      <c r="O479" t="s">
+        <v>3295</v>
+      </c>
+      <c r="P479" s="6" t="s">
+        <v>3296</v>
+      </c>
+      <c r="Q479">
+        <v>759550564</v>
+      </c>
+      <c r="R479" t="s">
+        <v>3297</v>
+      </c>
+      <c r="S479" s="1">
+        <v>46164.02920138889</v>
+      </c>
+      <c r="V479" t="s">
+        <v>29</v>
+      </c>
+      <c r="X479" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z479" t="s">
+        <v>3298</v>
+      </c>
+      <c r="AA479">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="480" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B480">
+        <v>5</v>
+      </c>
+      <c r="C480" t="s">
+        <v>3299</v>
+      </c>
+      <c r="D480">
+        <v>-0.19850619999999999</v>
+      </c>
+      <c r="E480">
+        <v>-78.505337900000001</v>
+      </c>
+      <c r="F480">
+        <v>0</v>
+      </c>
+      <c r="G480">
+        <v>5</v>
+      </c>
+      <c r="H480" t="s">
+        <v>33</v>
+      </c>
+      <c r="I480" t="s">
+        <v>28</v>
+      </c>
+      <c r="J480">
+        <v>10.5</v>
+      </c>
+      <c r="M480" t="s">
+        <v>189</v>
+      </c>
+      <c r="N480" t="s">
+        <v>3300</v>
+      </c>
+      <c r="O480" t="s">
+        <v>3301</v>
+      </c>
+      <c r="P480" s="6" t="s">
+        <v>3302</v>
+      </c>
+      <c r="Q480">
+        <v>759551014</v>
+      </c>
+      <c r="R480" t="s">
+        <v>3303</v>
+      </c>
+      <c r="S480" s="1">
+        <v>46164.030717592592</v>
+      </c>
+      <c r="V480" t="s">
+        <v>29</v>
+      </c>
+      <c r="X480" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z480" t="s">
+        <v>3304</v>
+      </c>
+      <c r="AA480">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="481" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B481">
+        <v>5</v>
+      </c>
+      <c r="C481" t="s">
+        <v>3305</v>
+      </c>
+      <c r="D481">
+        <v>-0.1987245</v>
+      </c>
+      <c r="E481">
+        <v>-78.505969899999997</v>
+      </c>
+      <c r="F481">
+        <v>0</v>
+      </c>
+      <c r="G481">
+        <v>5</v>
+      </c>
+      <c r="H481" t="s">
+        <v>33</v>
+      </c>
+      <c r="I481" t="s">
+        <v>28</v>
+      </c>
+      <c r="J481">
+        <v>9.5</v>
+      </c>
+      <c r="K481">
+        <v>50</v>
+      </c>
+      <c r="L481" t="s">
+        <v>874</v>
+      </c>
+      <c r="M481" t="s">
+        <v>187</v>
+      </c>
+      <c r="N481" t="s">
+        <v>3306</v>
+      </c>
+      <c r="O481" t="s">
+        <v>3307</v>
+      </c>
+      <c r="P481" s="6" t="s">
+        <v>3308</v>
+      </c>
+      <c r="Q481">
+        <v>759551896</v>
+      </c>
+      <c r="R481" t="s">
+        <v>3309</v>
+      </c>
+      <c r="S481" s="1">
+        <v>46164.03328703704</v>
+      </c>
+      <c r="V481" t="s">
+        <v>29</v>
+      </c>
+      <c r="X481" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z481" t="s">
+        <v>3310</v>
+      </c>
+      <c r="AA481">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="482" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B482">
+        <v>5</v>
+      </c>
+      <c r="C482" t="s">
+        <v>3311</v>
+      </c>
+      <c r="D482">
+        <v>-0.19902320000000001</v>
+      </c>
+      <c r="E482">
+        <v>-78.505920000000003</v>
+      </c>
+      <c r="F482">
+        <v>0</v>
+      </c>
+      <c r="G482">
+        <v>5</v>
+      </c>
+      <c r="H482" t="s">
+        <v>33</v>
+      </c>
+      <c r="I482" t="s">
+        <v>28</v>
+      </c>
+      <c r="J482">
+        <v>9.5</v>
+      </c>
+      <c r="K482">
+        <v>223</v>
+      </c>
+      <c r="L482" t="s">
+        <v>874</v>
+      </c>
+      <c r="M482" t="s">
+        <v>187</v>
+      </c>
+      <c r="N482" t="s">
+        <v>3312</v>
+      </c>
+      <c r="O482" t="s">
+        <v>3313</v>
+      </c>
+      <c r="P482" s="6" t="s">
+        <v>3314</v>
+      </c>
+      <c r="Q482">
+        <v>759552387</v>
+      </c>
+      <c r="R482" t="s">
+        <v>3315</v>
+      </c>
+      <c r="S482" s="1">
+        <v>46164.034745370373</v>
+      </c>
+      <c r="V482" t="s">
+        <v>29</v>
+      </c>
+      <c r="X482" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z482" t="s">
+        <v>3316</v>
+      </c>
+      <c r="AA482">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="483" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B483">
+        <v>5</v>
+      </c>
+      <c r="C483" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D483">
+        <v>-0.19931589999999999</v>
+      </c>
+      <c r="E483">
+        <v>-78.505828500000007</v>
+      </c>
+      <c r="F483">
+        <v>0</v>
+      </c>
+      <c r="G483">
+        <v>5</v>
+      </c>
+      <c r="H483" t="s">
+        <v>33</v>
+      </c>
+      <c r="I483" t="s">
+        <v>28</v>
+      </c>
+      <c r="J483">
+        <v>9.5</v>
+      </c>
+      <c r="K483">
+        <v>76</v>
+      </c>
+      <c r="L483" t="s">
+        <v>874</v>
+      </c>
+      <c r="M483" t="s">
+        <v>187</v>
+      </c>
+      <c r="N483" t="s">
+        <v>3318</v>
+      </c>
+      <c r="O483" t="s">
+        <v>3319</v>
+      </c>
+      <c r="P483" s="6" t="s">
+        <v>3320</v>
+      </c>
+      <c r="Q483">
+        <v>759552948</v>
+      </c>
+      <c r="R483" t="s">
+        <v>3321</v>
+      </c>
+      <c r="S483" s="1">
+        <v>46164.036215277767</v>
+      </c>
+      <c r="V483" t="s">
+        <v>29</v>
+      </c>
+      <c r="X483" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z483" t="s">
+        <v>3322</v>
+      </c>
+      <c r="AA483">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="484" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B484">
+        <v>5</v>
+      </c>
+      <c r="C484" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D484">
+        <v>-0.19912579999999999</v>
+      </c>
+      <c r="E484">
+        <v>-78.5054892</v>
+      </c>
+      <c r="F484">
+        <v>0</v>
+      </c>
+      <c r="G484">
+        <v>5</v>
+      </c>
+      <c r="H484" t="s">
+        <v>27</v>
+      </c>
+      <c r="I484" t="s">
+        <v>28</v>
+      </c>
+      <c r="J484">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K484">
+        <v>155</v>
+      </c>
+      <c r="L484" t="s">
+        <v>874</v>
+      </c>
+      <c r="M484" t="s">
+        <v>187</v>
+      </c>
+      <c r="N484" t="s">
+        <v>3324</v>
+      </c>
+      <c r="O484" t="s">
+        <v>3325</v>
+      </c>
+      <c r="P484" s="6" t="s">
+        <v>3326</v>
+      </c>
+      <c r="Q484">
+        <v>759553510</v>
+      </c>
+      <c r="R484" t="s">
+        <v>3327</v>
+      </c>
+      <c r="S484" s="1">
+        <v>46164.038090277783</v>
+      </c>
+      <c r="V484" t="s">
+        <v>29</v>
+      </c>
+      <c r="X484" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z484" t="s">
+        <v>3328</v>
+      </c>
+      <c r="AA484">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="485" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B485">
+        <v>5</v>
+      </c>
+      <c r="C485" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D485">
+        <v>-0.1990789</v>
+      </c>
+      <c r="E485">
+        <v>-78.505354400000002</v>
+      </c>
+      <c r="F485">
+        <v>0</v>
+      </c>
+      <c r="G485">
+        <v>5</v>
+      </c>
+      <c r="H485" t="s">
+        <v>33</v>
+      </c>
+      <c r="I485" t="s">
+        <v>28</v>
+      </c>
+      <c r="J485">
+        <v>10.5</v>
+      </c>
+      <c r="K485">
+        <v>77</v>
+      </c>
+      <c r="L485" t="s">
+        <v>874</v>
+      </c>
+      <c r="M485" t="s">
+        <v>187</v>
+      </c>
+      <c r="N485" t="s">
+        <v>3330</v>
+      </c>
+      <c r="O485" t="s">
+        <v>3331</v>
+      </c>
+      <c r="P485" s="6" t="s">
+        <v>3332</v>
+      </c>
+      <c r="Q485">
+        <v>759554371</v>
+      </c>
+      <c r="R485" t="s">
+        <v>3333</v>
+      </c>
+      <c r="S485" s="1">
+        <v>46164.040729166663</v>
+      </c>
+      <c r="V485" t="s">
+        <v>29</v>
+      </c>
+      <c r="X485" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z485" t="s">
+        <v>3334</v>
+      </c>
+      <c r="AA485">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="486" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B486">
+        <v>5</v>
+      </c>
+      <c r="C486" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D486">
+        <v>-0.1991241</v>
+      </c>
+      <c r="E486">
+        <v>-78.505369099999996</v>
+      </c>
+      <c r="F486">
+        <v>0</v>
+      </c>
+      <c r="G486">
+        <v>5</v>
+      </c>
+      <c r="H486" t="s">
+        <v>33</v>
+      </c>
+      <c r="I486" t="s">
+        <v>28</v>
+      </c>
+      <c r="J486">
+        <v>10.5</v>
+      </c>
+      <c r="K486">
+        <v>46</v>
+      </c>
+      <c r="L486" t="s">
+        <v>874</v>
+      </c>
+      <c r="M486" t="s">
+        <v>187</v>
+      </c>
+      <c r="N486" t="s">
+        <v>3336</v>
+      </c>
+      <c r="O486" t="s">
+        <v>3337</v>
+      </c>
+      <c r="P486" s="6" t="s">
+        <v>3338</v>
+      </c>
+      <c r="Q486">
+        <v>759554785</v>
+      </c>
+      <c r="R486" t="s">
+        <v>3339</v>
+      </c>
+      <c r="S486" s="1">
+        <v>46164.04178240741</v>
+      </c>
+      <c r="V486" t="s">
+        <v>29</v>
+      </c>
+      <c r="X486" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z486" t="s">
+        <v>3340</v>
+      </c>
+      <c r="AA486">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="487" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B487">
+        <v>5</v>
+      </c>
+      <c r="C487" t="s">
+        <v>3341</v>
+      </c>
+      <c r="D487">
+        <v>-0.1990963</v>
+      </c>
+      <c r="E487">
+        <v>-78.504963099999998</v>
+      </c>
+      <c r="F487">
+        <v>0</v>
+      </c>
+      <c r="G487">
+        <v>5</v>
+      </c>
+      <c r="H487" t="s">
+        <v>33</v>
+      </c>
+      <c r="I487" t="s">
+        <v>28</v>
+      </c>
+      <c r="J487">
+        <v>10</v>
+      </c>
+      <c r="K487">
+        <v>71</v>
+      </c>
+      <c r="L487" t="s">
+        <v>874</v>
+      </c>
+      <c r="M487" t="s">
+        <v>187</v>
+      </c>
+      <c r="N487" t="s">
+        <v>3342</v>
+      </c>
+      <c r="O487" t="s">
+        <v>3343</v>
+      </c>
+      <c r="P487" s="6" t="s">
+        <v>3344</v>
+      </c>
+      <c r="Q487">
+        <v>759555263</v>
+      </c>
+      <c r="R487" t="s">
+        <v>3345</v>
+      </c>
+      <c r="S487" s="1">
+        <v>46164.043356481481</v>
+      </c>
+      <c r="V487" t="s">
+        <v>29</v>
+      </c>
+      <c r="X487" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z487" t="s">
+        <v>3346</v>
+      </c>
+      <c r="AA487">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="488" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B488">
+        <v>5</v>
+      </c>
+      <c r="C488" t="s">
+        <v>3347</v>
+      </c>
+      <c r="D488">
+        <v>-0.19905039999999999</v>
+      </c>
+      <c r="E488">
+        <v>-78.504979199999994</v>
+      </c>
+      <c r="F488">
+        <v>0</v>
+      </c>
+      <c r="G488">
+        <v>5</v>
+      </c>
+      <c r="H488" t="s">
+        <v>33</v>
+      </c>
+      <c r="I488" t="s">
+        <v>28</v>
+      </c>
+      <c r="J488">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K488">
+        <v>54</v>
+      </c>
+      <c r="L488" t="s">
+        <v>874</v>
+      </c>
+      <c r="M488" t="s">
+        <v>187</v>
+      </c>
+      <c r="N488" t="s">
+        <v>3348</v>
+      </c>
+      <c r="O488" t="s">
+        <v>3349</v>
+      </c>
+      <c r="P488" s="6" t="s">
+        <v>3350</v>
+      </c>
+      <c r="Q488">
+        <v>759555529</v>
+      </c>
+      <c r="R488" t="s">
+        <v>3351</v>
+      </c>
+      <c r="S488" s="1">
+        <v>46164.044259259259</v>
+      </c>
+      <c r="V488" t="s">
+        <v>29</v>
+      </c>
+      <c r="X488" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z488" t="s">
+        <v>3352</v>
+      </c>
+      <c r="AA488">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="489" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B489">
+        <v>5</v>
+      </c>
+      <c r="C489" t="s">
+        <v>3353</v>
+      </c>
+      <c r="D489">
+        <v>-0.19822300000000001</v>
+      </c>
+      <c r="E489">
+        <v>-78.505617000000001</v>
+      </c>
+      <c r="F489">
+        <v>0</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489" t="s">
+        <v>27</v>
+      </c>
+      <c r="I489" t="s">
+        <v>28</v>
+      </c>
+      <c r="J489">
+        <v>7.5</v>
+      </c>
+      <c r="M489" t="s">
+        <v>189</v>
+      </c>
+      <c r="N489" t="s">
+        <v>3354</v>
+      </c>
+      <c r="O489" t="s">
+        <v>3355</v>
+      </c>
+      <c r="P489" s="6" t="s">
+        <v>3356</v>
+      </c>
+      <c r="Q489">
+        <v>759556485</v>
+      </c>
+      <c r="R489" t="s">
+        <v>3357</v>
+      </c>
+      <c r="S489" s="1">
+        <v>46164.046701388892</v>
+      </c>
+      <c r="V489" t="s">
+        <v>29</v>
+      </c>
+      <c r="X489" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z489" t="s">
+        <v>3358</v>
+      </c>
+      <c r="AA489">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="490" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B490">
+        <v>5</v>
+      </c>
+      <c r="C490" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D490">
+        <v>-0.19798589999999999</v>
+      </c>
+      <c r="E490">
+        <v>-78.505241699999999</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490">
+        <v>5</v>
+      </c>
+      <c r="H490" t="s">
+        <v>33</v>
+      </c>
+      <c r="I490" t="s">
+        <v>28</v>
+      </c>
+      <c r="J490">
+        <v>10.5</v>
+      </c>
+      <c r="M490" t="s">
+        <v>189</v>
+      </c>
+      <c r="N490" t="s">
+        <v>3360</v>
+      </c>
+      <c r="O490" t="s">
+        <v>3361</v>
+      </c>
+      <c r="P490" s="6" t="s">
+        <v>3362</v>
+      </c>
+      <c r="Q490">
+        <v>759556836</v>
+      </c>
+      <c r="R490" t="s">
+        <v>3363</v>
+      </c>
+      <c r="S490" s="1">
+        <v>46164.047592592593</v>
+      </c>
+      <c r="V490" t="s">
+        <v>29</v>
+      </c>
+      <c r="X490" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z490" t="s">
+        <v>3364</v>
+      </c>
+      <c r="AA490">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="491" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B491">
+        <v>5</v>
+      </c>
+      <c r="C491" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D491">
+        <v>-0.19798589999999999</v>
+      </c>
+      <c r="E491">
+        <v>-78.505241699999999</v>
+      </c>
+      <c r="F491">
+        <v>0</v>
+      </c>
+      <c r="G491">
+        <v>5</v>
+      </c>
+      <c r="H491" t="s">
+        <v>27</v>
+      </c>
+      <c r="I491" t="s">
+        <v>28</v>
+      </c>
+      <c r="J491">
+        <v>7</v>
+      </c>
+      <c r="M491" t="s">
+        <v>189</v>
+      </c>
+      <c r="N491" t="s">
+        <v>3365</v>
+      </c>
+      <c r="O491" t="s">
+        <v>3366</v>
+      </c>
+      <c r="P491" s="6" t="s">
+        <v>3367</v>
+      </c>
+      <c r="Q491">
+        <v>759557343</v>
+      </c>
+      <c r="R491" t="s">
+        <v>3368</v>
+      </c>
+      <c r="S491" s="1">
+        <v>46164.049155092587</v>
+      </c>
+      <c r="V491" t="s">
+        <v>29</v>
+      </c>
+      <c r="X491" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z491" t="s">
+        <v>3369</v>
+      </c>
+      <c r="AA491">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="492" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B492">
+        <v>5</v>
+      </c>
+      <c r="C492" t="s">
+        <v>3370</v>
+      </c>
+      <c r="D492">
+        <v>-0.1979195</v>
+      </c>
+      <c r="E492">
+        <v>-78.505440530000001</v>
+      </c>
+      <c r="F492">
+        <v>0</v>
+      </c>
+      <c r="G492">
+        <v>5</v>
+      </c>
+      <c r="H492" t="s">
+        <v>27</v>
+      </c>
+      <c r="I492" t="s">
+        <v>28</v>
+      </c>
+      <c r="J492">
+        <v>8.4</v>
+      </c>
+      <c r="M492" t="s">
+        <v>189</v>
+      </c>
+      <c r="N492" t="s">
+        <v>3354</v>
+      </c>
+      <c r="O492" t="s">
+        <v>3371</v>
+      </c>
+      <c r="P492" s="6" t="s">
+        <v>3372</v>
+      </c>
+      <c r="Q492">
+        <v>759557580</v>
+      </c>
+      <c r="R492" t="s">
+        <v>3373</v>
+      </c>
+      <c r="S492" s="1">
+        <v>46164.049895833326</v>
+      </c>
+      <c r="V492" t="s">
+        <v>29</v>
+      </c>
+      <c r="X492" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z492" t="s">
+        <v>3374</v>
+      </c>
+      <c r="AA492">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="493" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B493">
+        <v>5</v>
+      </c>
+      <c r="C493" t="s">
+        <v>3376</v>
+      </c>
+      <c r="D493">
+        <v>-0.19911999999999999</v>
+      </c>
+      <c r="E493">
+        <v>-78.505993000000004</v>
+      </c>
+      <c r="F493">
+        <v>2884.800048828125</v>
+      </c>
+      <c r="G493">
+        <v>21.267999649047852</v>
+      </c>
+      <c r="H493" t="s">
+        <v>33</v>
+      </c>
+      <c r="I493" t="s">
+        <v>28</v>
+      </c>
+      <c r="J493">
+        <v>10.5</v>
+      </c>
+      <c r="K493">
+        <v>88</v>
+      </c>
+      <c r="L493" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M493" t="s">
+        <v>187</v>
+      </c>
+      <c r="N493" t="s">
+        <v>3377</v>
+      </c>
+      <c r="O493" t="s">
+        <v>3378</v>
+      </c>
+      <c r="P493" s="6" t="s">
+        <v>3379</v>
+      </c>
+      <c r="Q493">
+        <v>768756706</v>
+      </c>
+      <c r="R493" t="s">
+        <v>3380</v>
+      </c>
+      <c r="S493" s="1">
+        <v>46175.597395833327</v>
+      </c>
+      <c r="V493" t="s">
+        <v>29</v>
+      </c>
+      <c r="X493" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z493" t="s">
+        <v>3381</v>
+      </c>
+      <c r="AA493">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="494" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B494">
+        <v>5</v>
+      </c>
+      <c r="C494" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D494">
+        <v>-0.19739999999999999</v>
+      </c>
+      <c r="E494">
+        <v>-78.506192999999996</v>
+      </c>
+      <c r="F494">
+        <v>2880.60009765625</v>
+      </c>
+      <c r="G494">
+        <v>17.23800086975098</v>
+      </c>
+      <c r="H494" t="s">
+        <v>33</v>
+      </c>
+      <c r="I494" t="s">
+        <v>28</v>
+      </c>
+      <c r="J494">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="M494" t="s">
+        <v>189</v>
+      </c>
+      <c r="N494" t="s">
+        <v>3384</v>
+      </c>
+      <c r="O494" t="s">
+        <v>3385</v>
+      </c>
+      <c r="P494" s="6" t="s">
+        <v>3386</v>
+      </c>
+      <c r="Q494">
+        <v>768757122</v>
+      </c>
+      <c r="R494" t="s">
+        <v>3387</v>
+      </c>
+      <c r="S494" s="1">
+        <v>46175.597731481481</v>
+      </c>
+      <c r="V494" t="s">
+        <v>29</v>
+      </c>
+      <c r="X494" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z494" t="s">
+        <v>3388</v>
+      </c>
+      <c r="AA494">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="495" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B495">
+        <v>5</v>
+      </c>
+      <c r="C495" t="s">
+        <v>3389</v>
+      </c>
+      <c r="D495">
+        <v>-0.19744100000000001</v>
+      </c>
+      <c r="E495">
+        <v>-78.506642999999997</v>
+      </c>
+      <c r="F495">
+        <v>2886.7001953125</v>
+      </c>
+      <c r="G495">
+        <v>17.559000015258789</v>
+      </c>
+      <c r="H495" t="s">
+        <v>33</v>
+      </c>
+      <c r="I495" t="s">
+        <v>28</v>
+      </c>
+      <c r="J495">
+        <v>10</v>
+      </c>
+      <c r="M495" t="s">
+        <v>189</v>
+      </c>
+      <c r="N495" t="s">
+        <v>3390</v>
+      </c>
+      <c r="O495" t="s">
+        <v>3391</v>
+      </c>
+      <c r="P495" s="6" t="s">
+        <v>3392</v>
+      </c>
+      <c r="Q495">
+        <v>768757252</v>
+      </c>
+      <c r="R495" t="s">
+        <v>3393</v>
+      </c>
+      <c r="S495" s="1">
+        <v>46175.59784722222</v>
+      </c>
+      <c r="V495" t="s">
+        <v>29</v>
+      </c>
+      <c r="X495" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z495" t="s">
+        <v>3394</v>
+      </c>
+      <c r="AA495">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="496" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B496">
+        <v>6</v>
+      </c>
+      <c r="C496" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D496">
+        <v>-0.19745099999999999</v>
+      </c>
+      <c r="E496">
+        <v>-78.506997999999996</v>
+      </c>
+      <c r="F496">
+        <v>2889.2001953125</v>
+      </c>
+      <c r="G496">
+        <v>31.777999877929691</v>
+      </c>
+      <c r="H496" t="s">
+        <v>33</v>
+      </c>
+      <c r="I496" t="s">
+        <v>28</v>
+      </c>
+      <c r="J496">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M496" t="s">
+        <v>189</v>
+      </c>
+      <c r="N496" t="s">
+        <v>3396</v>
+      </c>
+      <c r="O496" t="s">
+        <v>3397</v>
+      </c>
+      <c r="P496" s="6" t="s">
+        <v>3398</v>
+      </c>
+      <c r="Q496">
+        <v>768757399</v>
+      </c>
+      <c r="R496" t="s">
+        <v>3399</v>
+      </c>
+      <c r="S496" s="1">
+        <v>46175.597962962973</v>
+      </c>
+      <c r="V496" t="s">
+        <v>29</v>
+      </c>
+      <c r="X496" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z496" t="s">
+        <v>3400</v>
+      </c>
+      <c r="AA496">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="497" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B497">
+        <v>5</v>
+      </c>
+      <c r="C497" t="s">
+        <v>3401</v>
+      </c>
+      <c r="D497">
+        <v>-0.198327</v>
+      </c>
+      <c r="E497">
+        <v>-78.506163999999998</v>
+      </c>
+      <c r="F497">
+        <v>2883.2001953125</v>
+      </c>
+      <c r="G497">
+        <v>26.13699913024902</v>
+      </c>
+      <c r="H497" t="s">
+        <v>27</v>
+      </c>
+      <c r="I497" t="s">
+        <v>28</v>
+      </c>
+      <c r="J497">
+        <v>8.17</v>
+      </c>
+      <c r="M497" t="s">
+        <v>189</v>
+      </c>
+      <c r="N497" t="s">
+        <v>3402</v>
+      </c>
+      <c r="O497" t="s">
+        <v>3403</v>
+      </c>
+      <c r="P497" s="6" t="s">
+        <v>3404</v>
+      </c>
+      <c r="Q497">
+        <v>768757859</v>
+      </c>
+      <c r="R497" t="s">
+        <v>3405</v>
+      </c>
+      <c r="S497" s="1">
+        <v>46175.598298611112</v>
+      </c>
+      <c r="V497" t="s">
+        <v>29</v>
+      </c>
+      <c r="X497" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z497" t="s">
+        <v>3406</v>
+      </c>
+      <c r="AA497">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="498" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B498">
+        <v>5</v>
+      </c>
+      <c r="C498" t="s">
+        <v>3407</v>
+      </c>
+      <c r="D498">
+        <v>-0.19852</v>
+      </c>
+      <c r="E498">
+        <v>-78.506255999999993</v>
+      </c>
+      <c r="F498">
+        <v>2884.300048828125</v>
+      </c>
+      <c r="G498">
+        <v>19.235000610351559</v>
+      </c>
+      <c r="H498" t="s">
+        <v>27</v>
+      </c>
+      <c r="I498" t="s">
+        <v>60</v>
+      </c>
+      <c r="J498">
+        <v>7.7</v>
+      </c>
+      <c r="M498" t="s">
+        <v>189</v>
+      </c>
+      <c r="N498" t="s">
+        <v>3408</v>
+      </c>
+      <c r="O498" t="s">
+        <v>3409</v>
+      </c>
+      <c r="P498" s="6" t="s">
+        <v>3410</v>
+      </c>
+      <c r="Q498">
+        <v>768758025</v>
+      </c>
+      <c r="R498" t="s">
+        <v>3411</v>
+      </c>
+      <c r="S498" s="1">
+        <v>46175.598414351851</v>
+      </c>
+      <c r="V498" t="s">
+        <v>29</v>
+      </c>
+      <c r="X498" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z498" t="s">
+        <v>3412</v>
+      </c>
+      <c r="AA498">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="499" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B499">
+        <v>5</v>
+      </c>
+      <c r="C499" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D499">
+        <v>-0.19855400000000001</v>
+      </c>
+      <c r="E499">
+        <v>-78.506304</v>
+      </c>
+      <c r="F499">
+        <v>2884.400146484375</v>
+      </c>
+      <c r="G499">
+        <v>18.156000137329102</v>
+      </c>
+      <c r="H499" t="s">
+        <v>33</v>
+      </c>
+      <c r="I499" t="s">
+        <v>28</v>
+      </c>
+      <c r="J499">
+        <v>11.3</v>
+      </c>
+      <c r="K499">
+        <v>24</v>
+      </c>
+      <c r="L499" t="s">
+        <v>3414</v>
+      </c>
+      <c r="M499" t="s">
+        <v>187</v>
+      </c>
+      <c r="N499" t="s">
+        <v>3415</v>
+      </c>
+      <c r="O499" t="s">
+        <v>3416</v>
+      </c>
+      <c r="P499" s="6" t="s">
+        <v>3417</v>
+      </c>
+      <c r="Q499">
+        <v>768758265</v>
+      </c>
+      <c r="R499" t="s">
+        <v>3418</v>
+      </c>
+      <c r="S499" s="1">
+        <v>46175.598622685182</v>
+      </c>
+      <c r="V499" t="s">
+        <v>29</v>
+      </c>
+      <c r="X499" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z499" t="s">
+        <v>3419</v>
+      </c>
+      <c r="AA499">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="500" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B500">
+        <v>5</v>
+      </c>
+      <c r="C500" t="s">
+        <v>3420</v>
+      </c>
+      <c r="D500">
+        <v>-0.199132</v>
+      </c>
+      <c r="E500">
+        <v>-78.505894999999995</v>
+      </c>
+      <c r="F500">
+        <v>2891.2001953125</v>
+      </c>
+      <c r="G500">
+        <v>15.01399993896484</v>
+      </c>
+      <c r="H500" t="s">
+        <v>33</v>
+      </c>
+      <c r="I500" t="s">
+        <v>28</v>
+      </c>
+      <c r="J500">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K500">
+        <v>48</v>
+      </c>
+      <c r="L500" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M500" t="s">
+        <v>187</v>
+      </c>
+      <c r="N500" t="s">
+        <v>3421</v>
+      </c>
+      <c r="O500" t="s">
+        <v>3422</v>
+      </c>
+      <c r="P500" s="6" t="s">
+        <v>3423</v>
+      </c>
+      <c r="Q500">
+        <v>768758598</v>
+      </c>
+      <c r="R500" t="s">
+        <v>3424</v>
+      </c>
+      <c r="S500" s="1">
+        <v>46175.598900462966</v>
+      </c>
+      <c r="V500" t="s">
+        <v>29</v>
+      </c>
+      <c r="X500" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z500" t="s">
+        <v>3425</v>
+      </c>
+      <c r="AA500">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="501" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B501">
+        <v>5</v>
+      </c>
+      <c r="C501" t="s">
+        <v>3426</v>
+      </c>
+      <c r="D501">
+        <v>-0.19874800000000001</v>
+      </c>
+      <c r="E501">
+        <v>-78.506632999999994</v>
+      </c>
+      <c r="F501">
+        <v>2888.400146484375</v>
+      </c>
+      <c r="G501">
+        <v>22.64999961853027</v>
+      </c>
+      <c r="H501" t="s">
+        <v>33</v>
+      </c>
+      <c r="I501" t="s">
+        <v>28</v>
+      </c>
+      <c r="J501">
+        <v>10.3</v>
+      </c>
+      <c r="K501">
+        <v>50</v>
+      </c>
+      <c r="L501" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M501" t="s">
+        <v>187</v>
+      </c>
+      <c r="N501" t="s">
+        <v>3427</v>
+      </c>
+      <c r="O501" t="s">
+        <v>3428</v>
+      </c>
+      <c r="P501" s="6" t="s">
+        <v>3429</v>
+      </c>
+      <c r="Q501">
+        <v>768758744</v>
+      </c>
+      <c r="R501" t="s">
+        <v>3430</v>
+      </c>
+      <c r="S501" s="1">
+        <v>46175.599016203712</v>
+      </c>
+      <c r="V501" t="s">
+        <v>29</v>
+      </c>
+      <c r="X501" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z501" t="s">
+        <v>3431</v>
+      </c>
+      <c r="AA501">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="502" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B502">
+        <v>5</v>
+      </c>
+      <c r="C502" t="s">
+        <v>3432</v>
+      </c>
+      <c r="D502">
+        <v>-0.19869899999999999</v>
+      </c>
+      <c r="E502">
+        <v>-78.506923999999998</v>
+      </c>
+      <c r="F502">
+        <v>2892.2001953125</v>
+      </c>
+      <c r="G502">
+        <v>24.13800048828125</v>
+      </c>
+      <c r="H502" t="s">
+        <v>27</v>
+      </c>
+      <c r="I502" t="s">
+        <v>28</v>
+      </c>
+      <c r="J502">
+        <v>7.45</v>
+      </c>
+      <c r="K502">
+        <v>130</v>
+      </c>
+      <c r="L502" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M502" t="s">
+        <v>189</v>
+      </c>
+      <c r="N502" t="s">
+        <v>3433</v>
+      </c>
+      <c r="O502" t="s">
+        <v>3434</v>
+      </c>
+      <c r="P502" s="6" t="s">
+        <v>3435</v>
+      </c>
+      <c r="Q502">
+        <v>768758967</v>
+      </c>
+      <c r="R502" t="s">
+        <v>3436</v>
+      </c>
+      <c r="S502" s="1">
+        <v>46175.59920138889</v>
+      </c>
+      <c r="V502" t="s">
+        <v>29</v>
+      </c>
+      <c r="X502" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z502" t="s">
+        <v>3437</v>
+      </c>
+      <c r="AA502">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="503" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B503">
+        <v>5</v>
+      </c>
+      <c r="C503" t="s">
+        <v>3438</v>
+      </c>
+      <c r="D503">
+        <v>-0.198573</v>
+      </c>
+      <c r="E503">
+        <v>-78.507103999999998</v>
+      </c>
+      <c r="F503">
+        <v>2892.60009765625</v>
+      </c>
+      <c r="G503">
+        <v>23.808000564575199</v>
+      </c>
+      <c r="H503" t="s">
+        <v>27</v>
+      </c>
+      <c r="I503" t="s">
+        <v>28</v>
+      </c>
+      <c r="J503">
+        <v>11.5</v>
+      </c>
+      <c r="M503" t="s">
+        <v>189</v>
+      </c>
+      <c r="N503" t="s">
+        <v>3439</v>
+      </c>
+      <c r="O503" t="s">
+        <v>3440</v>
+      </c>
+      <c r="P503" s="6" t="s">
+        <v>3441</v>
+      </c>
+      <c r="Q503">
+        <v>768759134</v>
+      </c>
+      <c r="R503" t="s">
+        <v>3442</v>
+      </c>
+      <c r="S503" s="1">
+        <v>46175.599351851852</v>
+      </c>
+      <c r="V503" t="s">
+        <v>29</v>
+      </c>
+      <c r="X503" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z503" t="s">
+        <v>3443</v>
+      </c>
+      <c r="AA503">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="504" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B504">
+        <v>5</v>
+      </c>
+      <c r="C504" t="s">
+        <v>3444</v>
+      </c>
+      <c r="D504">
+        <v>-0.19860700000000001</v>
+      </c>
+      <c r="E504">
+        <v>-78.507062000000005</v>
+      </c>
+      <c r="F504">
+        <v>2892.60009765625</v>
+      </c>
+      <c r="G504">
+        <v>22.194000244140621</v>
+      </c>
+      <c r="H504" t="s">
+        <v>33</v>
+      </c>
+      <c r="I504" t="s">
+        <v>28</v>
+      </c>
+      <c r="J504">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K504">
+        <v>110</v>
+      </c>
+      <c r="L504" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M504" t="s">
+        <v>187</v>
+      </c>
+      <c r="N504" t="s">
+        <v>3445</v>
+      </c>
+      <c r="O504" t="s">
+        <v>3446</v>
+      </c>
+      <c r="P504" s="6" t="s">
+        <v>3447</v>
+      </c>
+      <c r="Q504">
+        <v>768759574</v>
+      </c>
+      <c r="R504" t="s">
+        <v>3448</v>
+      </c>
+      <c r="S504" s="1">
+        <v>46175.599687499998</v>
+      </c>
+      <c r="V504" t="s">
+        <v>29</v>
+      </c>
+      <c r="X504" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z504" t="s">
+        <v>3449</v>
+      </c>
+      <c r="AA504">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="505" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B505">
+        <v>5</v>
+      </c>
+      <c r="C505" t="s">
+        <v>3450</v>
+      </c>
+      <c r="D505">
+        <v>-0.19875899999999999</v>
+      </c>
+      <c r="E505">
+        <v>-78.507434000000003</v>
+      </c>
+      <c r="F505">
+        <v>2892.60009765625</v>
+      </c>
+      <c r="G505">
+        <v>51.069999694824219</v>
+      </c>
+      <c r="H505" t="s">
+        <v>33</v>
+      </c>
+      <c r="I505" t="s">
+        <v>28</v>
+      </c>
+      <c r="J505">
+        <v>11.85</v>
+      </c>
+      <c r="K505">
+        <v>29</v>
+      </c>
+      <c r="L505" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M505" t="s">
+        <v>187</v>
+      </c>
+      <c r="N505" t="s">
+        <v>3451</v>
+      </c>
+      <c r="O505" t="s">
+        <v>3452</v>
+      </c>
+      <c r="P505" s="6" t="s">
+        <v>3453</v>
+      </c>
+      <c r="Q505">
+        <v>768759865</v>
+      </c>
+      <c r="R505" t="s">
+        <v>3454</v>
+      </c>
+      <c r="S505" s="1">
+        <v>46175.59988425926</v>
+      </c>
+      <c r="V505" t="s">
+        <v>29</v>
+      </c>
+      <c r="X505" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z505" t="s">
+        <v>3455</v>
+      </c>
+      <c r="AA505">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="506" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B506">
+        <v>5</v>
+      </c>
+      <c r="C506" t="s">
+        <v>3456</v>
+      </c>
+      <c r="D506">
+        <v>-0.198458</v>
+      </c>
+      <c r="E506">
+        <v>-78.507142999999999</v>
+      </c>
+      <c r="F506">
+        <v>2889.000244140625</v>
+      </c>
+      <c r="G506">
+        <v>38.706001281738281</v>
+      </c>
+      <c r="H506" t="s">
+        <v>33</v>
+      </c>
+      <c r="I506" t="s">
+        <v>28</v>
+      </c>
+      <c r="J506">
+        <v>11.15</v>
+      </c>
+      <c r="K506">
+        <v>107</v>
+      </c>
+      <c r="L506" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M506" t="s">
+        <v>187</v>
+      </c>
+      <c r="N506" t="s">
+        <v>3457</v>
+      </c>
+      <c r="O506" t="s">
+        <v>3458</v>
+      </c>
+      <c r="P506" s="6" t="s">
+        <v>3459</v>
+      </c>
+      <c r="Q506">
+        <v>768760184</v>
+      </c>
+      <c r="R506" t="s">
+        <v>3460</v>
+      </c>
+      <c r="S506" s="1">
+        <v>46175.600069444437</v>
+      </c>
+      <c r="V506" t="s">
+        <v>29</v>
+      </c>
+      <c r="X506" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z506" t="s">
+        <v>3461</v>
+      </c>
+      <c r="AA506">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="507" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B507">
+        <v>5</v>
+      </c>
+      <c r="C507" t="s">
+        <v>3462</v>
+      </c>
+      <c r="D507">
+        <v>-0.198465</v>
+      </c>
+      <c r="E507">
+        <v>-78.507142000000002</v>
+      </c>
+      <c r="F507">
+        <v>2893.500244140625</v>
+      </c>
+      <c r="G507">
+        <v>37.455001831054688</v>
+      </c>
+      <c r="H507" t="s">
+        <v>27</v>
+      </c>
+      <c r="I507" t="s">
+        <v>28</v>
+      </c>
+      <c r="J507">
+        <v>10.8</v>
+      </c>
+      <c r="M507" t="s">
+        <v>189</v>
+      </c>
+      <c r="N507" t="s">
+        <v>3463</v>
+      </c>
+      <c r="O507" t="s">
+        <v>3464</v>
+      </c>
+      <c r="P507" s="6" t="s">
+        <v>3465</v>
+      </c>
+      <c r="Q507">
+        <v>768760477</v>
+      </c>
+      <c r="R507" t="s">
+        <v>3466</v>
+      </c>
+      <c r="S507" s="1">
+        <v>46175.600266203714</v>
+      </c>
+      <c r="V507" t="s">
+        <v>29</v>
+      </c>
+      <c r="X507" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z507" t="s">
+        <v>3467</v>
+      </c>
+      <c r="AA507">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="508" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B508">
+        <v>5</v>
+      </c>
+      <c r="C508" t="s">
+        <v>3468</v>
+      </c>
+      <c r="D508">
+        <v>-0.198544</v>
+      </c>
+      <c r="E508">
+        <v>-78.506865000000005</v>
+      </c>
+      <c r="F508">
+        <v>2888.500244140625</v>
+      </c>
+      <c r="G508">
+        <v>24.358999252319339</v>
+      </c>
+      <c r="H508" t="s">
+        <v>27</v>
+      </c>
+      <c r="I508" t="s">
+        <v>28</v>
+      </c>
+      <c r="J508">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K508">
+        <v>70</v>
+      </c>
+      <c r="L508" t="s">
+        <v>3469</v>
+      </c>
+      <c r="M508" t="s">
+        <v>187</v>
+      </c>
+      <c r="N508" t="s">
+        <v>3470</v>
+      </c>
+      <c r="O508" t="s">
+        <v>3471</v>
+      </c>
+      <c r="P508" s="6" t="s">
+        <v>3472</v>
+      </c>
+      <c r="Q508">
+        <v>768760641</v>
+      </c>
+      <c r="R508" t="s">
+        <v>3473</v>
+      </c>
+      <c r="S508" s="1">
+        <v>46175.600381944438</v>
+      </c>
+      <c r="V508" t="s">
+        <v>29</v>
+      </c>
+      <c r="X508" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z508" t="s">
+        <v>3474</v>
+      </c>
+      <c r="AA508">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="509" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B509">
+        <v>5</v>
+      </c>
+      <c r="C509" t="s">
+        <v>3475</v>
+      </c>
+      <c r="D509">
+        <v>-0.19856199999999999</v>
+      </c>
+      <c r="E509">
+        <v>-78.506529</v>
+      </c>
+      <c r="F509">
+        <v>2888.7001953125</v>
+      </c>
+      <c r="G509">
+        <v>19.408000946044918</v>
+      </c>
+      <c r="H509" t="s">
+        <v>27</v>
+      </c>
+      <c r="I509" t="s">
+        <v>28</v>
+      </c>
+      <c r="J509">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M509" t="s">
+        <v>189</v>
+      </c>
+      <c r="N509" t="s">
+        <v>3476</v>
+      </c>
+      <c r="O509" t="s">
+        <v>3477</v>
+      </c>
+      <c r="P509" s="6" t="s">
+        <v>3478</v>
+      </c>
+      <c r="Q509">
+        <v>768760853</v>
+      </c>
+      <c r="R509" t="s">
+        <v>3479</v>
+      </c>
+      <c r="S509" s="1">
+        <v>46175.600532407407</v>
+      </c>
+      <c r="V509" t="s">
+        <v>29</v>
+      </c>
+      <c r="X509" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z509" t="s">
+        <v>3480</v>
+      </c>
+      <c r="AA509">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="510" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B510">
+        <v>5</v>
+      </c>
+      <c r="C510" t="s">
+        <v>3481</v>
+      </c>
+      <c r="D510">
+        <v>-0.19849800000000001</v>
+      </c>
+      <c r="E510">
+        <v>-78.506697000000003</v>
+      </c>
+      <c r="F510">
+        <v>2888.900146484375</v>
+      </c>
+      <c r="G510">
+        <v>40.299999237060547</v>
+      </c>
+      <c r="H510" t="s">
+        <v>27</v>
+      </c>
+      <c r="I510" t="s">
+        <v>28</v>
+      </c>
+      <c r="J510">
+        <v>8</v>
+      </c>
+      <c r="M510" t="s">
+        <v>189</v>
+      </c>
+      <c r="N510" t="s">
+        <v>3482</v>
+      </c>
+      <c r="O510" t="s">
+        <v>3483</v>
+      </c>
+      <c r="P510" s="6" t="s">
+        <v>3484</v>
+      </c>
+      <c r="Q510">
+        <v>768761060</v>
+      </c>
+      <c r="R510" t="s">
+        <v>3485</v>
+      </c>
+      <c r="S510" s="1">
+        <v>46175.600706018522</v>
+      </c>
+      <c r="V510" t="s">
+        <v>29</v>
+      </c>
+      <c r="X510" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z510" t="s">
+        <v>3486</v>
+      </c>
+      <c r="AA510">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="511" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B511">
+        <v>5</v>
+      </c>
+      <c r="C511" t="s">
+        <v>3487</v>
+      </c>
+      <c r="D511">
+        <v>-0.19853999999999999</v>
+      </c>
+      <c r="E511">
+        <v>-78.506856999999997</v>
+      </c>
+      <c r="F511">
+        <v>2893.500244140625</v>
+      </c>
+      <c r="G511">
+        <v>19.107000350952148</v>
+      </c>
+      <c r="H511" t="s">
+        <v>27</v>
+      </c>
+      <c r="J511">
+        <v>6.9</v>
+      </c>
+      <c r="M511" t="s">
+        <v>189</v>
+      </c>
+      <c r="N511" t="s">
+        <v>3488</v>
+      </c>
+      <c r="O511" t="s">
+        <v>3489</v>
+      </c>
+      <c r="P511" s="6" t="s">
+        <v>3490</v>
+      </c>
+      <c r="Q511">
+        <v>768761384</v>
+      </c>
+      <c r="R511" t="s">
+        <v>3491</v>
+      </c>
+      <c r="S511" s="1">
+        <v>46175.600972222222</v>
+      </c>
+      <c r="V511" t="s">
+        <v>29</v>
+      </c>
+      <c r="X511" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z511" t="s">
+        <v>3492</v>
+      </c>
+      <c r="AA511">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="512" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B512">
+        <v>5</v>
+      </c>
+      <c r="C512" t="s">
+        <v>3493</v>
+      </c>
+      <c r="D512">
+        <v>-0.198213</v>
+      </c>
+      <c r="E512">
+        <v>-78.506922000000003</v>
+      </c>
+      <c r="F512">
+        <v>2889.000244140625</v>
+      </c>
+      <c r="G512">
+        <v>40.900001525878913</v>
+      </c>
+      <c r="H512" t="s">
+        <v>33</v>
+      </c>
+      <c r="I512" t="s">
+        <v>28</v>
+      </c>
+      <c r="J512">
+        <v>10.4</v>
+      </c>
+      <c r="K512">
+        <v>30</v>
+      </c>
+      <c r="L512" t="s">
+        <v>2382</v>
+      </c>
+      <c r="M512" t="s">
+        <v>187</v>
+      </c>
+      <c r="N512" t="s">
+        <v>3494</v>
+      </c>
+      <c r="O512" t="s">
+        <v>3495</v>
+      </c>
+      <c r="P512" s="6" t="s">
+        <v>3496</v>
+      </c>
+      <c r="Q512">
+        <v>768761711</v>
+      </c>
+      <c r="R512" t="s">
+        <v>3497</v>
+      </c>
+      <c r="S512" s="1">
+        <v>46175.601203703707</v>
+      </c>
+      <c r="V512" t="s">
+        <v>29</v>
+      </c>
+      <c r="X512" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z512" t="s">
+        <v>3498</v>
+      </c>
+      <c r="AA512">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="513" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B513">
+        <v>5</v>
+      </c>
+      <c r="C513" t="s">
+        <v>3499</v>
+      </c>
+      <c r="D513">
+        <v>-0.19817599999999999</v>
+      </c>
+      <c r="E513">
+        <v>-78.507180000000005</v>
+      </c>
+      <c r="F513">
+        <v>2888.900146484375</v>
+      </c>
+      <c r="G513">
+        <v>49.034000396728523</v>
+      </c>
+      <c r="H513" t="s">
+        <v>27</v>
+      </c>
+      <c r="I513" t="s">
+        <v>28</v>
+      </c>
+      <c r="J513">
+        <v>6.5</v>
+      </c>
+      <c r="M513" t="s">
+        <v>189</v>
+      </c>
+      <c r="N513" t="s">
+        <v>3500</v>
+      </c>
+      <c r="O513" t="s">
+        <v>3501</v>
+      </c>
+      <c r="P513" s="6" t="s">
+        <v>3502</v>
+      </c>
+      <c r="Q513">
+        <v>768762214</v>
+      </c>
+      <c r="R513" t="s">
+        <v>3503</v>
+      </c>
+      <c r="S513" s="1">
+        <v>46175.601574074077</v>
+      </c>
+      <c r="V513" t="s">
+        <v>29</v>
+      </c>
+      <c r="X513" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z513" t="s">
+        <v>3504</v>
+      </c>
+      <c r="AA513">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="514" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B514">
+        <v>5</v>
+      </c>
+      <c r="C514" t="s">
+        <v>3505</v>
+      </c>
+      <c r="D514">
+        <v>-0.19770199999999999</v>
+      </c>
+      <c r="E514">
+        <v>-78.507028000000005</v>
+      </c>
+      <c r="F514">
+        <v>2889.2001953125</v>
+      </c>
+      <c r="G514">
+        <v>32.386001586914063</v>
+      </c>
+      <c r="H514" t="s">
+        <v>27</v>
+      </c>
+      <c r="I514" t="s">
+        <v>28</v>
+      </c>
+      <c r="J514">
+        <v>3.7</v>
+      </c>
+      <c r="M514" t="s">
+        <v>189</v>
+      </c>
+      <c r="N514" t="s">
+        <v>3506</v>
+      </c>
+      <c r="O514" t="s">
+        <v>3507</v>
+      </c>
+      <c r="P514" s="6" t="s">
+        <v>3508</v>
+      </c>
+      <c r="Q514">
+        <v>770201879</v>
+      </c>
+      <c r="R514" t="s">
+        <v>3509</v>
+      </c>
+      <c r="S514" s="1">
+        <v>46176.914907407408</v>
+      </c>
+      <c r="V514" t="s">
+        <v>29</v>
+      </c>
+      <c r="X514" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z514" t="s">
+        <v>3510</v>
+      </c>
+      <c r="AA514">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="515" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B515">
+        <v>5</v>
+      </c>
+      <c r="C515" t="s">
+        <v>3511</v>
+      </c>
+      <c r="D515">
+        <v>-0.197853</v>
+      </c>
+      <c r="E515">
+        <v>-78.506842000000006</v>
+      </c>
+      <c r="F515">
+        <v>2888.900146484375</v>
+      </c>
+      <c r="G515">
+        <v>7.3990001678466797</v>
+      </c>
+      <c r="H515" t="s">
+        <v>27</v>
+      </c>
+      <c r="I515" t="s">
+        <v>28</v>
+      </c>
+      <c r="J515">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M515" t="s">
+        <v>189</v>
+      </c>
+      <c r="N515" t="s">
+        <v>3512</v>
+      </c>
+      <c r="O515" t="s">
+        <v>3513</v>
+      </c>
+      <c r="P515" s="6" t="s">
+        <v>3514</v>
+      </c>
+      <c r="Q515">
+        <v>770201932</v>
+      </c>
+      <c r="R515" t="s">
+        <v>3515</v>
+      </c>
+      <c r="S515" s="1">
+        <v>46176.915011574078</v>
+      </c>
+      <c r="V515" t="s">
+        <v>29</v>
+      </c>
+      <c r="X515" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z515" t="s">
+        <v>3516</v>
+      </c>
+      <c r="AA515">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="516" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B516">
+        <v>5</v>
+      </c>
+      <c r="C516" t="s">
+        <v>3517</v>
+      </c>
+      <c r="D516">
+        <v>-0.197994</v>
+      </c>
+      <c r="E516">
+        <v>-78.506836000000007</v>
+      </c>
+      <c r="F516">
+        <v>2888.900146484375</v>
+      </c>
+      <c r="G516">
+        <v>16.218000411987301</v>
+      </c>
+      <c r="H516" t="s">
+        <v>27</v>
+      </c>
+      <c r="I516" t="s">
+        <v>28</v>
+      </c>
+      <c r="J516">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M516" t="s">
+        <v>189</v>
+      </c>
+      <c r="N516" t="s">
+        <v>3518</v>
+      </c>
+      <c r="O516" t="s">
+        <v>3519</v>
+      </c>
+      <c r="P516" s="6" t="s">
+        <v>3520</v>
+      </c>
+      <c r="Q516">
+        <v>770201989</v>
+      </c>
+      <c r="R516" t="s">
+        <v>3521</v>
+      </c>
+      <c r="S516" s="1">
+        <v>46176.91511574074</v>
+      </c>
+      <c r="V516" t="s">
+        <v>29</v>
+      </c>
+      <c r="X516" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z516" t="s">
+        <v>3522</v>
+      </c>
+      <c r="AA516">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="517" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B517">
+        <v>5</v>
+      </c>
+      <c r="C517" t="s">
+        <v>3523</v>
+      </c>
+      <c r="D517">
+        <v>-0.19774800000000001</v>
+      </c>
+      <c r="E517">
+        <v>-78.506771999999998</v>
+      </c>
+      <c r="F517">
+        <v>2888.900146484375</v>
+      </c>
+      <c r="G517">
+        <v>7.3990001678466797</v>
+      </c>
+      <c r="H517" t="s">
+        <v>27</v>
+      </c>
+      <c r="I517" t="s">
+        <v>28</v>
+      </c>
+      <c r="J517">
+        <v>6.4</v>
+      </c>
+      <c r="M517" t="s">
+        <v>189</v>
+      </c>
+      <c r="N517" t="s">
+        <v>3524</v>
+      </c>
+      <c r="O517" t="s">
+        <v>3525</v>
+      </c>
+      <c r="P517" s="6" t="s">
+        <v>3526</v>
+      </c>
+      <c r="Q517">
+        <v>770202012</v>
+      </c>
+      <c r="R517" t="s">
+        <v>3527</v>
+      </c>
+      <c r="S517" s="1">
+        <v>46176.915173611109</v>
+      </c>
+      <c r="V517" t="s">
+        <v>29</v>
+      </c>
+      <c r="X517" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z517" t="s">
+        <v>3528</v>
+      </c>
+      <c r="AA517">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="518" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B518">
+        <v>5</v>
+      </c>
+      <c r="C518" t="s">
+        <v>3529</v>
+      </c>
+      <c r="D518">
+        <v>-0.19808799999999999</v>
+      </c>
+      <c r="E518">
+        <v>-78.506694999999993</v>
+      </c>
+      <c r="F518">
+        <v>2888.7001953125</v>
+      </c>
+      <c r="G518">
+        <v>8.2390003204345703</v>
+      </c>
+      <c r="H518" t="s">
+        <v>27</v>
+      </c>
+      <c r="I518" t="s">
+        <v>28</v>
+      </c>
+      <c r="J518">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M518" t="s">
+        <v>189</v>
+      </c>
+      <c r="N518" t="s">
+        <v>3530</v>
+      </c>
+      <c r="O518" t="s">
+        <v>3531</v>
+      </c>
+      <c r="P518" s="6" t="s">
+        <v>3532</v>
+      </c>
+      <c r="Q518">
+        <v>770202059</v>
+      </c>
+      <c r="R518" t="s">
+        <v>3533</v>
+      </c>
+      <c r="S518" s="1">
+        <v>46176.915254629632</v>
+      </c>
+      <c r="V518" t="s">
+        <v>29</v>
+      </c>
+      <c r="X518" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z518" t="s">
+        <v>3534</v>
+      </c>
+      <c r="AA518">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -41228,8 +46868,74 @@
     <hyperlink ref="P450" r:id="rId449" xr:uid="{7E8B13B2-ABCD-465B-AA37-CDAE93BE2E78}"/>
     <hyperlink ref="P451" r:id="rId450" xr:uid="{91E8F081-61EC-4F0B-8523-62DCE1609AD8}"/>
     <hyperlink ref="P452" r:id="rId451" xr:uid="{F0EB279C-CA30-4F30-A8F4-B8B6E147FD6D}"/>
+    <hyperlink ref="P453" r:id="rId452" xr:uid="{DE8F1683-ECF3-4F71-BFB7-BF5B16E69275}"/>
+    <hyperlink ref="P454" r:id="rId453" xr:uid="{562D701E-F635-48BA-BF67-30C3C8B969E7}"/>
+    <hyperlink ref="P455" r:id="rId454" xr:uid="{8A2F6452-DB30-4C6B-A53C-735E7142084B}"/>
+    <hyperlink ref="P456" r:id="rId455" xr:uid="{F34BE8BA-FF9E-487C-888D-7AF972CFB688}"/>
+    <hyperlink ref="P457" r:id="rId456" xr:uid="{AB9C9E58-1B01-49E8-80F6-B2998041938E}"/>
+    <hyperlink ref="P458" r:id="rId457" xr:uid="{126A3EFB-7E26-4FA0-BDC7-D5C26BA076D9}"/>
+    <hyperlink ref="P459" r:id="rId458" xr:uid="{0ABCA765-F4BA-4107-8369-DDD4E3E27679}"/>
+    <hyperlink ref="P460" r:id="rId459" xr:uid="{C4AD005B-0E9C-4631-B1F7-10352FEF8F4A}"/>
+    <hyperlink ref="P461" r:id="rId460" xr:uid="{3AE74C42-2B88-44F0-8A36-5017DF4B77BC}"/>
+    <hyperlink ref="P462" r:id="rId461" xr:uid="{6C7E83C8-E1A6-40DD-B3DD-863F566D1E62}"/>
+    <hyperlink ref="P463" r:id="rId462" xr:uid="{F6FD0651-B909-404C-87D9-F898FEA14D08}"/>
+    <hyperlink ref="P464" r:id="rId463" xr:uid="{AF1F3229-9582-46AF-A202-D585F359890E}"/>
+    <hyperlink ref="P465" r:id="rId464" xr:uid="{FF55F4A5-0C34-4FAC-9DA7-A6A7DE43AA5F}"/>
+    <hyperlink ref="P466" r:id="rId465" xr:uid="{D5445651-C6D2-470A-A90C-0CA20252A9BE}"/>
+    <hyperlink ref="P467" r:id="rId466" xr:uid="{B53D0B22-1AB8-4B7D-B0D1-315D8D1E8840}"/>
+    <hyperlink ref="P468" r:id="rId467" xr:uid="{9B3A61A6-C312-47DB-BBE1-81480DEAF468}"/>
+    <hyperlink ref="P469" r:id="rId468" xr:uid="{CEB6D588-A80B-42EA-BF5B-F81EC1C7E882}"/>
+    <hyperlink ref="P470" r:id="rId469" xr:uid="{7FA7BBED-F590-4784-88AE-B929AFCA19B5}"/>
+    <hyperlink ref="P471" r:id="rId470" xr:uid="{54447C59-B57E-4018-91F3-8BB4165F57CD}"/>
+    <hyperlink ref="P472" r:id="rId471" xr:uid="{E6FC4338-AF91-4DED-AB60-52373AC5B60A}"/>
+    <hyperlink ref="P473" r:id="rId472" xr:uid="{457143AF-09A7-4813-BC4D-C5D80ADC2E6C}"/>
+    <hyperlink ref="P474" r:id="rId473" xr:uid="{F915C067-3EC5-4CD5-9C0A-CF6C92906B84}"/>
+    <hyperlink ref="P475" r:id="rId474" xr:uid="{E3E9F21A-60B9-455F-B42F-EC40AE7DD9EB}"/>
+    <hyperlink ref="P476" r:id="rId475" xr:uid="{0BED7006-8323-4A22-A053-5B9961EEF952}"/>
+    <hyperlink ref="P477" r:id="rId476" xr:uid="{DF0391A1-FF46-4B00-8241-DBBF67065502}"/>
+    <hyperlink ref="P478" r:id="rId477" xr:uid="{AEAC826E-06AA-4F09-B24F-827C87962F23}"/>
+    <hyperlink ref="P479" r:id="rId478" xr:uid="{F2743E92-B67A-40A5-AB68-487AA5AA740C}"/>
+    <hyperlink ref="P480" r:id="rId479" xr:uid="{154A7366-71A8-47E1-8C6F-6D52861FDE59}"/>
+    <hyperlink ref="P481" r:id="rId480" xr:uid="{2713D9D5-9522-4A61-9C4A-9BF4E321404F}"/>
+    <hyperlink ref="P482" r:id="rId481" xr:uid="{A429E533-921A-48CF-933B-BFB62C5F3121}"/>
+    <hyperlink ref="P483" r:id="rId482" xr:uid="{DC35E749-3694-40D5-9608-99E5E5AF8AED}"/>
+    <hyperlink ref="P484" r:id="rId483" xr:uid="{2CE01BFD-2C38-4845-8610-EFCB05C1CB8E}"/>
+    <hyperlink ref="P485" r:id="rId484" xr:uid="{FA9A8CDC-2E59-4422-AE99-C635E5CA8D65}"/>
+    <hyperlink ref="P486" r:id="rId485" xr:uid="{36791C0A-2A38-4DC3-B39C-5A5AA8A113BE}"/>
+    <hyperlink ref="P487" r:id="rId486" xr:uid="{7E830D96-30EB-4729-887C-3B0EFD5FDF10}"/>
+    <hyperlink ref="P488" r:id="rId487" xr:uid="{FBED9E47-2299-43FF-8238-228BBA675CD2}"/>
+    <hyperlink ref="P489" r:id="rId488" xr:uid="{5E5EA240-69AB-4950-A611-929BDD86467B}"/>
+    <hyperlink ref="P490" r:id="rId489" xr:uid="{B9A36773-715E-45FD-ACCA-7A17BB104B73}"/>
+    <hyperlink ref="P491" r:id="rId490" xr:uid="{5DD21592-05DD-4AEE-8B45-60051554FB4A}"/>
+    <hyperlink ref="P492" r:id="rId491" xr:uid="{67E3D7C6-6169-4CC3-9199-A378F502FDB2}"/>
+    <hyperlink ref="P493" r:id="rId492" xr:uid="{FFB7E54A-1904-4C3C-AE30-0AE12CF3C544}"/>
+    <hyperlink ref="P494" r:id="rId493" xr:uid="{1ECA9869-261A-4363-B1EB-503E8500ECDD}"/>
+    <hyperlink ref="P495" r:id="rId494" xr:uid="{4AB55652-6DEA-44B2-9E2E-7D9919DE3E6E}"/>
+    <hyperlink ref="P496" r:id="rId495" xr:uid="{975DE79A-65CF-44C6-86A0-EEAB016A4D74}"/>
+    <hyperlink ref="P497" r:id="rId496" xr:uid="{81EA7155-04F3-40A4-9DC2-706F21821F64}"/>
+    <hyperlink ref="P498" r:id="rId497" xr:uid="{A3418F58-F45B-4FFA-9C32-A9DBA9F37F91}"/>
+    <hyperlink ref="P499" r:id="rId498" xr:uid="{8DE9FA1C-220E-4121-B496-BC7DF1F4B3CC}"/>
+    <hyperlink ref="P500" r:id="rId499" xr:uid="{D9880A91-88F2-4BE5-99FF-78521D55E3CC}"/>
+    <hyperlink ref="P501" r:id="rId500" xr:uid="{6B59FF03-0C8F-49B9-90D3-D4CBCE610994}"/>
+    <hyperlink ref="P502" r:id="rId501" xr:uid="{5AE43B55-70D4-4BC4-88CD-6283073B27D9}"/>
+    <hyperlink ref="P503" r:id="rId502" xr:uid="{B4263DEE-9EE9-4E2A-B5D4-B9491128F8DC}"/>
+    <hyperlink ref="P504" r:id="rId503" xr:uid="{1EB26F65-071C-4BA9-9BE6-7653378040AC}"/>
+    <hyperlink ref="P505" r:id="rId504" xr:uid="{81CC2F47-7421-41A9-B3E9-4C01589F8D2B}"/>
+    <hyperlink ref="P506" r:id="rId505" xr:uid="{349D286B-5CF8-4ABD-B929-594C58BC6423}"/>
+    <hyperlink ref="P507" r:id="rId506" xr:uid="{2601FE3C-09C7-43FD-8C74-63DE6DC95713}"/>
+    <hyperlink ref="P508" r:id="rId507" xr:uid="{A28C054D-4B0B-4A54-9EDE-2655EEB95E01}"/>
+    <hyperlink ref="P509" r:id="rId508" xr:uid="{68987FDD-BA38-4C28-9CDF-F3AB5808D4BD}"/>
+    <hyperlink ref="P510" r:id="rId509" xr:uid="{CC21E93B-6533-4FF8-994A-19D04BF3004D}"/>
+    <hyperlink ref="P511" r:id="rId510" xr:uid="{A31AE5EB-05B9-46A1-A479-F58CC4509A35}"/>
+    <hyperlink ref="P512" r:id="rId511" xr:uid="{DF2619BB-ADF4-404D-8648-EE0E1C5340A7}"/>
+    <hyperlink ref="P513" r:id="rId512" xr:uid="{610E23D0-A471-4913-8054-93603D61BA98}"/>
+    <hyperlink ref="P514" r:id="rId513" xr:uid="{799850AF-1600-4A9A-9051-2BC92E526CB6}"/>
+    <hyperlink ref="P515" r:id="rId514" xr:uid="{343D0824-426F-485F-8808-4E0A0F05CA49}"/>
+    <hyperlink ref="P516" r:id="rId515" xr:uid="{DC30CB3E-2015-4217-86CC-EE37704B7C9F}"/>
+    <hyperlink ref="P517" r:id="rId516" xr:uid="{3D383B90-14EF-4542-B6B5-79F64BE79B11}"/>
+    <hyperlink ref="P518" r:id="rId517" xr:uid="{008DE945-9BEC-4886-A0B3-F6731C7AC677}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId452"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId518"/>
 </worksheet>
 </file>